--- a/docs/Wajenzi-Modules-List.xlsx
+++ b/docs/Wajenzi-Modules-List.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="602">
   <si>
     <t>#</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>PHASE 1 — Foundation &amp; Core Operations  (Oct 2024 – Apr 2025)</t>
+    <t>PHASE 1 — Foundation &amp; Core Operations  (Oct 2024 – Apr 2025)  —  TZS 2,500,000</t>
   </si>
   <si>
     <t>Settings &amp; Configuration</t>
@@ -63,7 +63,7 @@
 (Wk 1 – 5)</t>
   </si>
   <si>
-    <t>TZS 17,000,000</t>
+    <t>230,000</t>
   </si>
   <si>
     <t>Complete</t>
@@ -142,7 +142,7 @@
 (Wk 3 – 10)</t>
   </si>
   <si>
-    <t>TZS 14,500,000</t>
+    <t>195,000</t>
   </si>
   <si>
     <t>Employee Documents</t>
@@ -200,7 +200,7 @@
 (Wk 5 – 16)</t>
   </si>
   <si>
-    <t>TZS 26,000,000</t>
+    <t>460,000</t>
   </si>
   <si>
     <t>Journal Entries</t>
@@ -300,6 +300,9 @@
 (Wk 9 – 15)</t>
   </si>
   <si>
+    <t>310,000</t>
+  </si>
+  <si>
     <t>NSSF Contributions</t>
   </si>
   <si>
@@ -367,7 +370,7 @@
 (Wk 11 – 22)</t>
   </si>
   <si>
-    <t>TZS 30,000,000</t>
+    <t>385,000</t>
   </si>
   <si>
     <t>Leave Management</t>
@@ -449,7 +452,7 @@
 (Wk 13 – 20)</t>
   </si>
   <si>
-    <t>TZS 19,500,000</t>
+    <t>270,000</t>
   </si>
   <si>
     <t>Purchase VAT Register</t>
@@ -516,7 +519,7 @@
 (Wk 18 – 23)</t>
   </si>
   <si>
-    <t>TZS 13,000,000</t>
+    <t>155,000</t>
   </si>
   <si>
     <t>Project Expenses</t>
@@ -611,9 +614,6 @@
 (Wk 24 – 30)</t>
   </si>
   <si>
-    <t>TZS 15,500,000</t>
-  </si>
-  <si>
     <t>Project Reports</t>
   </si>
   <si>
@@ -684,7 +684,7 @@
 (Wk 26 – 30)</t>
   </si>
   <si>
-    <t>TZS 11,500,000</t>
+    <t>145,000</t>
   </si>
   <si>
     <t>Sidebar Navigation</t>
@@ -720,16 +720,22 @@
     <t>53 Sub-Modules</t>
   </si>
   <si>
+    <t>Complete: TZS 2,500,000</t>
+  </si>
+  <si>
+    <t>In Process: TZS 0</t>
+  </si>
+  <si>
     <t>Oct 2024 – Apr 2025</t>
   </si>
   <si>
-    <t>TZS 177,000,000</t>
-  </si>
-  <si>
-    <t>10 Complete</t>
-  </si>
-  <si>
-    <t>PHASE 2 — Project Management &amp; Client Services  (Apr 2025 – Sep 2025)</t>
+    <t>2,500,000</t>
+  </si>
+  <si>
+    <t>Paid: 1,782,031.25</t>
+  </si>
+  <si>
+    <t>PHASE 2 — Project Management &amp; Client Services  (Apr 2025 – Sep 2025)  —  TZS 1,850,000</t>
   </si>
   <si>
     <t>BOQ Templates</t>
@@ -791,7 +797,7 @@
 (Wk 30 – 44)</t>
   </si>
   <si>
-    <t>TZS 39,000,000</t>
+    <t>540,000</t>
   </si>
   <si>
     <t>Project BOQ</t>
@@ -889,7 +895,7 @@
 (Wk 36 – 40)</t>
   </si>
   <si>
-    <t>TZS 9,000,000</t>
+    <t>115,000</t>
   </si>
   <si>
     <t>Installment Tracking</t>
@@ -976,7 +982,7 @@
 (Wk 42 – 46)</t>
   </si>
   <si>
-    <t>TZS 6,500,000</t>
+    <t>75,000</t>
   </si>
   <si>
     <t xml:space="preserve">Aug – Sep 2025
@@ -999,9 +1005,6 @@
 (Wk 46 – 52)</t>
   </si>
   <si>
-    <t>TZS 21,000,000</t>
-  </si>
-  <si>
     <t>BOQ Transparency</t>
   </si>
   <si>
@@ -1041,16 +1044,22 @@
     <t>48 Sub-Modules</t>
   </si>
   <si>
+    <t>Complete: TZS 1,270,000</t>
+  </si>
+  <si>
+    <t>In Process: TZS 580,000</t>
+  </si>
+  <si>
     <t>Apr 2025 – Sep 2025</t>
   </si>
   <si>
-    <t>TZS 137,500,000</t>
-  </si>
-  <si>
-    <t>6 Complete, 3 In Process</t>
-  </si>
-  <si>
-    <t>PHASE 3 — Advanced Operations &amp; Mobile  (Sep 2025 – Feb 2026)</t>
+    <t>1,850,000</t>
+  </si>
+  <si>
+    <t>Not Yet Paid</t>
+  </si>
+  <si>
+    <t>PHASE 3 — Advanced Operations &amp; Mobile  (Sep 2025 – Feb 2026)  —  TZS 2,270,000</t>
   </si>
   <si>
     <t>Billing &amp; Invoicing</t>
@@ -1072,9 +1081,6 @@
 (Wk 50 – 58)</t>
   </si>
   <si>
-    <t>TZS 24,500,000</t>
-  </si>
-  <si>
     <t>Proforma Invoices</t>
   </si>
   <si>
@@ -1142,9 +1148,6 @@
 (Wk 52 – 60)</t>
   </si>
   <si>
-    <t>TZS 28,500,000</t>
-  </si>
-  <si>
     <t>Supplier Quotations</t>
   </si>
   <si>
@@ -1200,9 +1203,6 @@
 (Wk 52 – 56)</t>
   </si>
   <si>
-    <t>TZS 10,500,000</t>
-  </si>
-  <si>
     <t>Labor Procurement</t>
   </si>
   <si>
@@ -1271,9 +1271,6 @@
 (Wk 58 – 62)</t>
   </si>
   <si>
-    <t>TZS 7,800,000</t>
-  </si>
-  <si>
     <t>Attendance System</t>
   </si>
   <si>
@@ -1293,9 +1290,6 @@
 (Wk 60 – 66)</t>
   </si>
   <si>
-    <t>TZS 18,000,000</t>
-  </si>
-  <si>
     <t>Daily Attendance</t>
   </si>
   <si>
@@ -1350,7 +1344,7 @@
 (Wk 56 – 70)</t>
   </si>
   <si>
-    <t>TZS 50,500,000</t>
+    <t>575,000</t>
   </si>
   <si>
     <t>Client Dashboard</t>
@@ -1395,28 +1389,142 @@
     <t>51 Sub-Modules</t>
   </si>
   <si>
+    <t>Complete: TZS 580,000</t>
+  </si>
+  <si>
+    <t>In Process: TZS 1,690,000</t>
+  </si>
+  <si>
     <t>Sep 2025 – Feb 2026</t>
   </si>
   <si>
-    <t>TZS 180,300,000</t>
-  </si>
-  <si>
-    <t>2 Complete, 7 In Process</t>
+    <t>2,270,000</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT TOTAL</t>
+  </si>
+  <si>
+    <t>20 Modules | 158 Sub-Modules</t>
+  </si>
+  <si>
+    <t>Complete: TZS 4,350,000</t>
+  </si>
+  <si>
+    <t>In Process: TZS 2,270,000</t>
+  </si>
+  <si>
+    <t>Oct 2024 – Feb 2026</t>
+  </si>
+  <si>
+    <t>6,620,000</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>TZS</t>
+  </si>
+  <si>
+    <t>Google Play Store — Staff App</t>
+  </si>
+  <si>
+    <t>$25</t>
+  </si>
+  <si>
+    <t>67,500</t>
+  </si>
+  <si>
+    <t>Google Play Store — Client App</t>
+  </si>
+  <si>
+    <t>Apple App Store — Staff App</t>
+  </si>
+  <si>
+    <t>$99</t>
+  </si>
+  <si>
+    <t>267,300</t>
+  </si>
+  <si>
+    <t>Apple App Store — Client App</t>
+  </si>
+  <si>
+    <t>Deployment Fee — Staff App</t>
+  </si>
+  <si>
+    <t>200,000</t>
+  </si>
+  <si>
+    <t>Deployment Fee — Client App</t>
+  </si>
+  <si>
+    <t>DEPLOYMENT TOTAL</t>
+  </si>
+  <si>
+    <t>1,069,600</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Total (TZS)</t>
+  </si>
+  <si>
+    <t>Paid (TZS)</t>
+  </si>
+  <si>
+    <t>Balance (TZS)</t>
+  </si>
+  <si>
+    <t>Phase 1 — Development Cost</t>
+  </si>
+  <si>
+    <t>2,500,000.00</t>
+  </si>
+  <si>
+    <t>1,782,031.25</t>
+  </si>
+  <si>
+    <t>717,968.75</t>
+  </si>
+  <si>
+    <t>Phase 2 — Development Cost</t>
+  </si>
+  <si>
+    <t>1,850,000.00</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>Phase 3 — Development Cost</t>
+  </si>
+  <si>
+    <t>2,270,000.00</t>
+  </si>
+  <si>
+    <t>App Deployment &amp; Store Fees</t>
+  </si>
+  <si>
+    <t>1,069,600.00</t>
   </si>
   <si>
     <t>GRAND TOTAL</t>
   </si>
   <si>
-    <t>20 Modules | 158 Sub-Modules</t>
-  </si>
-  <si>
-    <t>Oct 2024 – Feb 2026</t>
-  </si>
-  <si>
-    <t>TZS 494,800,000</t>
-  </si>
-  <si>
-    <t>18C / 10IP</t>
+    <t>7,689,600.00</t>
+  </si>
+  <si>
+    <t>5,907,568.75</t>
+  </si>
+  <si>
+    <t>TOTAL PAID</t>
+  </si>
+  <si>
+    <t>TOTAL UNPAID (BALANCE)</t>
   </si>
   <si>
     <t>Sub-Modules</t>
@@ -1738,16 +1846,13 @@
   </si>
   <si>
     <t>All web modules (API)</t>
-  </si>
-  <si>
-    <t>70 Weeks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1811,7 +1916,44 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF8E44AD"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF8E44AD"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC3545"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF82E0AA"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFF6B6B"/>
       <sz val="14"/>
     </font>
     <font>
@@ -1836,13 +1978,8 @@
       <color rgb="FFE67E22"/>
       <sz val="12"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="26">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1969,8 +2106,33 @@
         <fgColor rgb="FFFDEBD0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8E44AD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5EEF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8DAEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -2101,9 +2263,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF2E86C1"/>
+      <top style="medium">
+        <color rgb="FF8E44AD"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF8E44AD"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2124,27 +2288,18 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF27AE60"/>
+      <bottom style="medium">
+        <color rgb="FF8E44AD"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFE67E22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
+      <top style="medium">
         <color rgb="FF1B4F72"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color rgb="FF1B4F72"/>
       </bottom>
       <diagonal/>
@@ -2153,7 +2308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2173,6 +2328,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2188,6 +2346,9 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2200,6 +2361,9 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2212,6 +2376,9 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2224,6 +2391,9 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2236,6 +2406,9 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2248,6 +2421,9 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2260,178 +2436,277 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="20" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="21" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="22" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="23" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="24" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2773,7 +3048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I162"/>
+  <dimension ref="A1:I184"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2782,7 +3057,7 @@
     <col min="4" max="4" width="46" customWidth="1"/>
     <col min="5" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2850,10 +3125,10 @@
       <c r="G3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2873,8 +3148,8 @@
         <v>21</v>
       </c>
       <c r="G4" s="6"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
@@ -2892,8 +3167,8 @@
         <v>25</v>
       </c>
       <c r="G5" s="6"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="8"/>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
@@ -2911,8 +3186,8 @@
         <v>14</v>
       </c>
       <c r="G6" s="6"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
@@ -2930,8 +3205,8 @@
         <v>14</v>
       </c>
       <c r="G7" s="6"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
@@ -2949,113 +3224,113 @@
         <v>35</v>
       </c>
       <c r="G8" s="6"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="A9" s="9">
         <v>2</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="7"/>
+      <c r="F10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="8"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="7"/>
+      <c r="E11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="10" t="s">
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="10" t="s">
+      <c r="E12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="7"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="8"/>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="10" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="7"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="8"/>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -3079,10 +3354,10 @@
       <c r="G14" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3102,8 +3377,8 @@
         <v>65</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="8"/>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
@@ -3121,8 +3396,8 @@
         <v>69</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="8"/>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
@@ -3140,8 +3415,8 @@
         <v>72</v>
       </c>
       <c r="G17" s="6"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="8"/>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
@@ -3159,8 +3434,8 @@
         <v>76</v>
       </c>
       <c r="G18" s="6"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="8"/>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
@@ -3178,8 +3453,8 @@
         <v>80</v>
       </c>
       <c r="G19" s="6"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="8"/>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
@@ -3197,8 +3472,8 @@
         <v>83</v>
       </c>
       <c r="G20" s="6"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="8"/>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
@@ -3216,1008 +3491,1014 @@
         <v>87</v>
       </c>
       <c r="G21" s="6"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="8"/>
     </row>
     <row r="22" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
+      <c r="A22" s="14">
         <v>9</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="14"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="17"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="14"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="17"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="14"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" s="17"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="14"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="17"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
+        <v>7</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="19"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="22"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="19"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="G29" s="22"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="G30" s="22"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="8"/>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="19"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G31" s="22"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="8"/>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="G32" s="22"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="8"/>
+    </row>
+    <row r="33" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="24">
+        <v>3</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="F33" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="G33" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="24"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="G34" s="27"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="8"/>
+    </row>
+    <row r="35" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="24"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="F35" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="G35" s="27"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="8"/>
+    </row>
+    <row r="36" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="24"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F36" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="G36" s="27"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="8"/>
+    </row>
+    <row r="37" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="24"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F37" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="G37" s="27"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="8"/>
+    </row>
+    <row r="38" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="29">
+        <v>11</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="D38" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="E38" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="F38" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="G38" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="H38" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="29"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="E39" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="G39" s="32"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="8"/>
+    </row>
+    <row r="40" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="D40" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="G40" s="32"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="8"/>
+    </row>
+    <row r="41" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="29"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="D41" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="E41" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="F41" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="G41" s="32"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="8"/>
+    </row>
+    <row r="42" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="34">
+        <v>19</v>
+      </c>
+      <c r="B42" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C42" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="H42" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="34"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="F43" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="G43" s="37"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="8"/>
+    </row>
+    <row r="44" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="34"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="E44" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="G44" s="37"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="8"/>
+    </row>
+    <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="34"/>
+      <c r="B45" s="35"/>
+      <c r="C45" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="37"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="8"/>
+    </row>
+    <row r="46" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="24">
+        <v>15</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="F46" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="G46" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="H46" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="24"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F47" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="G47" s="27"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="8"/>
+    </row>
+    <row r="48" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="24"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="G48" s="27"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="8"/>
+    </row>
+    <row r="49" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="24"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="G49" s="27"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="8"/>
+    </row>
+    <row r="50" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="24"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="G50" s="27"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="8"/>
+    </row>
+    <row r="51" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="24"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="E51" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="F51" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="G51" s="27"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="8"/>
+    </row>
+    <row r="52" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="39">
+        <v>1</v>
+      </c>
+      <c r="B52" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="C52" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D52" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="E52" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="F52" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="G52" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="H52" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="39"/>
+      <c r="B53" s="40"/>
+      <c r="C53" s="41" t="s">
+        <v>221</v>
+      </c>
+      <c r="D53" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="E53" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="F53" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="42"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="8"/>
+    </row>
+    <row r="54" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="39"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="D54" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="E54" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="42"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="8"/>
+    </row>
+    <row r="55" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="39"/>
+      <c r="B55" s="40"/>
+      <c r="C55" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="D55" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="E55" s="41" t="s">
+        <v>228</v>
+      </c>
+      <c r="F55" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" s="42"/>
+      <c r="H55" s="43"/>
+      <c r="I55" s="8"/>
+    </row>
+    <row r="56" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="B56" s="44" t="s">
+        <v>230</v>
+      </c>
+      <c r="C56" s="44" t="s">
+        <v>231</v>
+      </c>
+      <c r="D56" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="E56" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="F56" s="44" t="s">
+        <v>233</v>
+      </c>
+      <c r="G56" s="44" t="s">
+        <v>234</v>
+      </c>
+      <c r="H56" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="I56" s="44" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="58" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="46" t="s">
+        <v>237</v>
+      </c>
+      <c r="B58" s="46"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="46"/>
+      <c r="I58" s="46"/>
+    </row>
+    <row r="59" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="34">
+        <v>6</v>
+      </c>
+      <c r="B59" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="C59" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="D59" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="E59" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="F59" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="H59" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I59" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="7"/>
-    </row>
-    <row r="24" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="7"/>
-    </row>
-    <row r="25" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="G25" s="15"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="7"/>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="7"/>
-    </row>
-    <row r="27" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
-        <v>7</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="I27" s="7" t="s">
+    <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="34"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="D60" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="E60" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" s="37"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="8"/>
+    </row>
+    <row r="61" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="34"/>
+      <c r="B61" s="35"/>
+      <c r="C61" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="D61" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="E61" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="F61" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="G61" s="37"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="8"/>
+    </row>
+    <row r="62" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="34"/>
+      <c r="B62" s="35"/>
+      <c r="C62" s="36" t="s">
+        <v>249</v>
+      </c>
+      <c r="D62" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="37"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="8"/>
+    </row>
+    <row r="63" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="47">
+        <v>4</v>
+      </c>
+      <c r="B63" s="48" t="s">
+        <v>251</v>
+      </c>
+      <c r="C63" s="49" t="s">
+        <v>252</v>
+      </c>
+      <c r="D63" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="E63" s="49" t="s">
+        <v>254</v>
+      </c>
+      <c r="F63" s="49" t="s">
+        <v>255</v>
+      </c>
+      <c r="G63" s="50" t="s">
+        <v>256</v>
+      </c>
+      <c r="H63" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="I63" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="G28" s="19"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="7"/>
-    </row>
-    <row r="29" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="G29" s="19"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="7"/>
-    </row>
-    <row r="30" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="16"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="G30" s="19"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="7"/>
-    </row>
-    <row r="31" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="G31" s="19"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="7"/>
-    </row>
-    <row r="32" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="G32" s="19"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="7"/>
-    </row>
-    <row r="33" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="20">
-        <v>3</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="G33" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="20"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="G34" s="23"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="7"/>
-    </row>
-    <row r="35" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="20"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="G35" s="23"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="7"/>
-    </row>
-    <row r="36" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="20"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G36" s="23"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="7"/>
-    </row>
-    <row r="37" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="20"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="F37" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="G37" s="23"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="7"/>
-    </row>
-    <row r="38" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="24">
-        <v>11</v>
-      </c>
-      <c r="B38" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C38" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="F38" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="G38" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="H38" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="E39" s="26" t="s">
+    <row r="64" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="47"/>
+      <c r="B64" s="48"/>
+      <c r="C64" s="49" t="s">
+        <v>258</v>
+      </c>
+      <c r="D64" s="49" t="s">
+        <v>259</v>
+      </c>
+      <c r="E64" s="49" t="s">
+        <v>260</v>
+      </c>
+      <c r="F64" s="49" t="s">
+        <v>261</v>
+      </c>
+      <c r="G64" s="50"/>
+      <c r="H64" s="51"/>
+      <c r="I64" s="8"/>
+    </row>
+    <row r="65" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="47"/>
+      <c r="B65" s="48"/>
+      <c r="C65" s="49" t="s">
+        <v>262</v>
+      </c>
+      <c r="D65" s="49" t="s">
+        <v>263</v>
+      </c>
+      <c r="E65" s="49" t="s">
+        <v>264</v>
+      </c>
+      <c r="F65" s="49" t="s">
+        <v>265</v>
+      </c>
+      <c r="G65" s="50"/>
+      <c r="H65" s="51"/>
+      <c r="I65" s="8"/>
+    </row>
+    <row r="66" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="47"/>
+      <c r="B66" s="48"/>
+      <c r="C66" s="49" t="s">
+        <v>266</v>
+      </c>
+      <c r="D66" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="E66" s="49" t="s">
+        <v>268</v>
+      </c>
+      <c r="F66" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="G66" s="50"/>
+      <c r="H66" s="51"/>
+      <c r="I66" s="8"/>
+    </row>
+    <row r="67" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="47"/>
+      <c r="B67" s="48"/>
+      <c r="C67" s="49" t="s">
+        <v>270</v>
+      </c>
+      <c r="D67" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="E67" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="F39" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="G39" s="27"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="7"/>
-    </row>
-    <row r="40" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="F40" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="27"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="7"/>
-    </row>
-    <row r="41" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="D41" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="F41" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="G41" s="27"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="7"/>
-    </row>
-    <row r="42" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="28">
-        <v>19</v>
-      </c>
-      <c r="B42" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="H42" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="28"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="D43" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="E43" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="F43" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="G43" s="31"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="7"/>
-    </row>
-    <row r="44" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="28"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="D44" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F44" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="G44" s="31"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="7"/>
-    </row>
-    <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="28"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="D45" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="E45" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45" s="31"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="7"/>
-    </row>
-    <row r="46" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="20">
-        <v>15</v>
-      </c>
-      <c r="B46" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="D46" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="F46" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="G46" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="H46" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="20"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="G47" s="23"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="7"/>
-    </row>
-    <row r="48" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="20"/>
-      <c r="B48" s="21"/>
-      <c r="C48" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F48" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="G48" s="23"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="7"/>
-    </row>
-    <row r="49" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="20"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="E49" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="G49" s="23"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="7"/>
-    </row>
-    <row r="50" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="20"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F50" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="G50" s="23"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="7"/>
-    </row>
-    <row r="51" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="20"/>
-      <c r="B51" s="21"/>
-      <c r="C51" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="E51" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="F51" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="G51" s="23"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="7"/>
-    </row>
-    <row r="52" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="32">
-        <v>1</v>
-      </c>
-      <c r="B52" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="C52" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="D52" s="34" t="s">
-        <v>216</v>
-      </c>
-      <c r="E52" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="F52" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="G52" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="H52" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="32"/>
-      <c r="B53" s="33"/>
-      <c r="C53" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="D53" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="E53" s="34" t="s">
-        <v>223</v>
-      </c>
-      <c r="F53" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G53" s="35"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="7"/>
-    </row>
-    <row r="54" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="32"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="34" t="s">
-        <v>224</v>
-      </c>
-      <c r="D54" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="E54" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" s="35"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="7"/>
-    </row>
-    <row r="55" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="32"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="D55" s="34" t="s">
-        <v>227</v>
-      </c>
-      <c r="E55" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="F55" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G55" s="35"/>
-      <c r="H55" s="33"/>
-      <c r="I55" s="7"/>
-    </row>
-    <row r="56" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="B56" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="C56" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36" t="s">
-        <v>232</v>
-      </c>
-      <c r="H56" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="I56" s="36" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="58" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="B58" s="38"/>
-      <c r="C58" s="38"/>
-      <c r="D58" s="38"/>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="38"/>
-      <c r="I58" s="38"/>
-    </row>
-    <row r="59" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="28">
-        <v>6</v>
-      </c>
-      <c r="B59" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="C59" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="D59" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="E59" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="F59" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="H59" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="28"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="D60" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="E60" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F60" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60" s="31"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="7"/>
-    </row>
-    <row r="61" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="28"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="30" t="s">
-        <v>243</v>
-      </c>
-      <c r="D61" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="E61" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="F61" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="G61" s="31"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="7"/>
-    </row>
-    <row r="62" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="28"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="D62" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="E62" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F62" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" s="31"/>
-      <c r="H62" s="29"/>
-      <c r="I62" s="7"/>
-    </row>
-    <row r="63" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="39">
-        <v>4</v>
-      </c>
-      <c r="B63" s="40" t="s">
-        <v>249</v>
-      </c>
-      <c r="C63" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="D63" s="41" t="s">
-        <v>251</v>
-      </c>
-      <c r="E63" s="41" t="s">
-        <v>252</v>
-      </c>
-      <c r="F63" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="G63" s="42" t="s">
-        <v>254</v>
-      </c>
-      <c r="H63" s="40" t="s">
-        <v>255</v>
-      </c>
-      <c r="I63" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="39"/>
-      <c r="B64" s="40"/>
-      <c r="C64" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="D64" s="41" t="s">
-        <v>257</v>
-      </c>
-      <c r="E64" s="41" t="s">
-        <v>258</v>
-      </c>
-      <c r="F64" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="G64" s="42"/>
-      <c r="H64" s="40"/>
-      <c r="I64" s="7"/>
-    </row>
-    <row r="65" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="39"/>
-      <c r="B65" s="40"/>
-      <c r="C65" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="D65" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="E65" s="41" t="s">
-        <v>262</v>
-      </c>
-      <c r="F65" s="41" t="s">
-        <v>263</v>
-      </c>
-      <c r="G65" s="42"/>
-      <c r="H65" s="40"/>
-      <c r="I65" s="7"/>
-    </row>
-    <row r="66" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="39"/>
-      <c r="B66" s="40"/>
-      <c r="C66" s="41" t="s">
-        <v>264</v>
-      </c>
-      <c r="D66" s="41" t="s">
-        <v>265</v>
-      </c>
-      <c r="E66" s="41" t="s">
-        <v>266</v>
-      </c>
-      <c r="F66" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="G66" s="42"/>
-      <c r="H66" s="40"/>
-      <c r="I66" s="7"/>
-    </row>
-    <row r="67" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="39"/>
-      <c r="B67" s="40"/>
-      <c r="C67" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="D67" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="E67" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="F67" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="G67" s="42"/>
-      <c r="H67" s="40"/>
-      <c r="I67" s="7"/>
+      <c r="F67" s="49" t="s">
+        <v>272</v>
+      </c>
+      <c r="G67" s="50"/>
+      <c r="H67" s="51"/>
+      <c r="I67" s="8"/>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="39"/>
-      <c r="B68" s="40"/>
-      <c r="C68" s="41" t="s">
-        <v>271</v>
-      </c>
-      <c r="D68" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="E68" s="41" t="s">
+      <c r="A68" s="47"/>
+      <c r="B68" s="48"/>
+      <c r="C68" s="49" t="s">
         <v>273</v>
       </c>
-      <c r="F68" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="42"/>
-      <c r="H68" s="40"/>
-      <c r="I68" s="7"/>
+      <c r="D68" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="E68" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="F68" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="50"/>
+      <c r="H68" s="51"/>
+      <c r="I68" s="8"/>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="39"/>
-      <c r="B69" s="40"/>
-      <c r="C69" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="D69" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="E69" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F69" s="41" t="s">
+      <c r="A69" s="47"/>
+      <c r="B69" s="48"/>
+      <c r="C69" s="49" t="s">
         <v>276</v>
       </c>
-      <c r="G69" s="42"/>
-      <c r="H69" s="40"/>
-      <c r="I69" s="7"/>
+      <c r="D69" s="49" t="s">
+        <v>277</v>
+      </c>
+      <c r="E69" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="G69" s="50"/>
+      <c r="H69" s="51"/>
+      <c r="I69" s="8"/>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="39"/>
-      <c r="B70" s="40"/>
-      <c r="C70" s="41" t="s">
-        <v>277</v>
-      </c>
-      <c r="D70" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="E70" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F70" s="41" t="s">
+      <c r="A70" s="47"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="49" t="s">
         <v>279</v>
       </c>
-      <c r="G70" s="42"/>
-      <c r="H70" s="40"/>
-      <c r="I70" s="7"/>
+      <c r="D70" s="49" t="s">
+        <v>280</v>
+      </c>
+      <c r="E70" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" s="49" t="s">
+        <v>281</v>
+      </c>
+      <c r="G70" s="50"/>
+      <c r="H70" s="51"/>
+      <c r="I70" s="8"/>
     </row>
     <row r="71" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
@@ -4239,12 +4520,12 @@
         <v>59</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="I71" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I71" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4264,8 +4545,8 @@
         <v>65</v>
       </c>
       <c r="G72" s="6"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="8"/>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
@@ -4283,8 +4564,8 @@
         <v>69</v>
       </c>
       <c r="G73" s="6"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="8"/>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
@@ -4302,8 +4583,8 @@
         <v>72</v>
       </c>
       <c r="G74" s="6"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="8"/>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
@@ -4321,8 +4602,8 @@
         <v>76</v>
       </c>
       <c r="G75" s="6"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="8"/>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
@@ -4340,8 +4621,8 @@
         <v>80</v>
       </c>
       <c r="G76" s="6"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="8"/>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
@@ -4359,8 +4640,8 @@
         <v>83</v>
       </c>
       <c r="G77" s="6"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="8"/>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
@@ -4378,161 +4659,161 @@
         <v>87</v>
       </c>
       <c r="G78" s="6"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="7"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="8"/>
     </row>
     <row r="79" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="43">
-        <v>14</v>
-      </c>
-      <c r="B79" s="44" t="s">
-        <v>281</v>
-      </c>
-      <c r="C79" s="45" t="s">
-        <v>282</v>
-      </c>
-      <c r="D79" s="45" t="s">
+      <c r="A79" s="52">
+        <v>14</v>
+      </c>
+      <c r="B79" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="E79" s="45" t="s">
+      <c r="C79" s="54" t="s">
         <v>284</v>
       </c>
-      <c r="F79" s="45" t="s">
+      <c r="D79" s="54" t="s">
         <v>285</v>
       </c>
-      <c r="G79" s="46" t="s">
+      <c r="E79" s="54" t="s">
         <v>286</v>
       </c>
-      <c r="H79" s="44" t="s">
+      <c r="F79" s="54" t="s">
         <v>287</v>
       </c>
-      <c r="I79" s="7" t="s">
+      <c r="G79" s="55" t="s">
+        <v>288</v>
+      </c>
+      <c r="H79" s="56" t="s">
+        <v>289</v>
+      </c>
+      <c r="I79" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="43"/>
-      <c r="B80" s="44"/>
-      <c r="C80" s="45" t="s">
-        <v>288</v>
-      </c>
-      <c r="D80" s="45" t="s">
-        <v>289</v>
-      </c>
-      <c r="E80" s="45" t="s">
+      <c r="A80" s="52"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="54" t="s">
         <v>290</v>
       </c>
-      <c r="F80" s="45" t="s">
+      <c r="D80" s="54" t="s">
         <v>291</v>
       </c>
-      <c r="G80" s="46"/>
-      <c r="H80" s="44"/>
-      <c r="I80" s="7"/>
+      <c r="E80" s="54" t="s">
+        <v>292</v>
+      </c>
+      <c r="F80" s="54" t="s">
+        <v>293</v>
+      </c>
+      <c r="G80" s="55"/>
+      <c r="H80" s="56"/>
+      <c r="I80" s="8"/>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="43"/>
-      <c r="B81" s="44"/>
-      <c r="C81" s="45" t="s">
-        <v>292</v>
-      </c>
-      <c r="D81" s="45" t="s">
-        <v>293</v>
-      </c>
-      <c r="E81" s="45" t="s">
+      <c r="A81" s="52"/>
+      <c r="B81" s="53"/>
+      <c r="C81" s="54" t="s">
         <v>294</v>
       </c>
-      <c r="F81" s="45" t="s">
+      <c r="D81" s="54" t="s">
         <v>295</v>
       </c>
-      <c r="G81" s="46"/>
-      <c r="H81" s="44"/>
-      <c r="I81" s="7"/>
+      <c r="E81" s="54" t="s">
+        <v>296</v>
+      </c>
+      <c r="F81" s="54" t="s">
+        <v>297</v>
+      </c>
+      <c r="G81" s="55"/>
+      <c r="H81" s="56"/>
+      <c r="I81" s="8"/>
     </row>
     <row r="82" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="47">
+      <c r="A82" s="57">
         <v>13</v>
       </c>
-      <c r="B82" s="48" t="s">
-        <v>296</v>
-      </c>
-      <c r="C82" s="49" t="s">
-        <v>297</v>
-      </c>
-      <c r="D82" s="49" t="s">
+      <c r="B82" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="E82" s="49" t="s">
+      <c r="C82" s="59" t="s">
         <v>299</v>
       </c>
-      <c r="F82" s="49" t="s">
+      <c r="D82" s="59" t="s">
         <v>300</v>
       </c>
-      <c r="G82" s="50" t="s">
+      <c r="E82" s="59" t="s">
         <v>301</v>
       </c>
-      <c r="H82" s="48" t="s">
-        <v>220</v>
-      </c>
-      <c r="I82" s="51" t="s">
+      <c r="F82" s="59" t="s">
         <v>302</v>
       </c>
+      <c r="G82" s="60" t="s">
+        <v>303</v>
+      </c>
+      <c r="H82" s="61" t="s">
+        <v>166</v>
+      </c>
+      <c r="I82" s="62" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="47"/>
-      <c r="B83" s="48"/>
-      <c r="C83" s="49" t="s">
-        <v>303</v>
-      </c>
-      <c r="D83" s="49" t="s">
-        <v>304</v>
-      </c>
-      <c r="E83" s="49" t="s">
+      <c r="A83" s="57"/>
+      <c r="B83" s="58"/>
+      <c r="C83" s="59" t="s">
         <v>305</v>
       </c>
-      <c r="F83" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="G83" s="50"/>
-      <c r="H83" s="48"/>
-      <c r="I83" s="51"/>
+      <c r="D83" s="59" t="s">
+        <v>306</v>
+      </c>
+      <c r="E83" s="59" t="s">
+        <v>307</v>
+      </c>
+      <c r="F83" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" s="60"/>
+      <c r="H83" s="61"/>
+      <c r="I83" s="62"/>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="47"/>
-      <c r="B84" s="48"/>
-      <c r="C84" s="49" t="s">
-        <v>306</v>
-      </c>
-      <c r="D84" s="49" t="s">
-        <v>307</v>
-      </c>
-      <c r="E84" s="49" t="s">
+      <c r="A84" s="57"/>
+      <c r="B84" s="58"/>
+      <c r="C84" s="59" t="s">
         <v>308</v>
       </c>
-      <c r="F84" s="49" t="s">
+      <c r="D84" s="59" t="s">
         <v>309</v>
       </c>
-      <c r="G84" s="50"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="51"/>
+      <c r="E84" s="59" t="s">
+        <v>310</v>
+      </c>
+      <c r="F84" s="59" t="s">
+        <v>311</v>
+      </c>
+      <c r="G84" s="60"/>
+      <c r="H84" s="61"/>
+      <c r="I84" s="62"/>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="47"/>
-      <c r="B85" s="48"/>
-      <c r="C85" s="49" t="s">
-        <v>310</v>
-      </c>
-      <c r="D85" s="49" t="s">
-        <v>311</v>
-      </c>
-      <c r="E85" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="F85" s="49" t="s">
+      <c r="A85" s="57"/>
+      <c r="B85" s="58"/>
+      <c r="C85" s="59" t="s">
         <v>312</v>
       </c>
-      <c r="G85" s="50"/>
-      <c r="H85" s="48"/>
-      <c r="I85" s="51"/>
+      <c r="D85" s="59" t="s">
+        <v>313</v>
+      </c>
+      <c r="E85" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85" s="59" t="s">
+        <v>314</v>
+      </c>
+      <c r="G85" s="60"/>
+      <c r="H85" s="61"/>
+      <c r="I85" s="62"/>
     </row>
     <row r="86" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
@@ -4554,12 +4835,12 @@
         <v>14</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="I86" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I86" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4579,8 +4860,8 @@
         <v>21</v>
       </c>
       <c r="G87" s="6"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="7"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="8"/>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
@@ -4598,8 +4879,8 @@
         <v>25</v>
       </c>
       <c r="G88" s="6"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="7"/>
+      <c r="H88" s="7"/>
+      <c r="I88" s="8"/>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
@@ -4617,8 +4898,8 @@
         <v>14</v>
       </c>
       <c r="G89" s="6"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="7"/>
+      <c r="H89" s="7"/>
+      <c r="I89" s="8"/>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
@@ -4636,8 +4917,8 @@
         <v>14</v>
       </c>
       <c r="G90" s="6"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="7"/>
+      <c r="H90" s="7"/>
+      <c r="I90" s="8"/>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
@@ -4655,874 +4936,880 @@
         <v>35</v>
       </c>
       <c r="G91" s="6"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="7"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="8"/>
     </row>
     <row r="92" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="32">
+      <c r="A92" s="39">
         <v>1</v>
       </c>
-      <c r="B92" s="33" t="s">
+      <c r="B92" s="40" t="s">
         <v>214</v>
       </c>
-      <c r="C92" s="34" t="s">
+      <c r="C92" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="D92" s="34" t="s">
+      <c r="D92" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="E92" s="34" t="s">
+      <c r="E92" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="F92" s="34" t="s">
+      <c r="F92" s="41" t="s">
         <v>218</v>
       </c>
-      <c r="G92" s="35" t="s">
-        <v>314</v>
-      </c>
-      <c r="H92" s="33" t="s">
-        <v>315</v>
-      </c>
-      <c r="I92" s="7" t="s">
+      <c r="G92" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="H92" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="I92" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="32"/>
-      <c r="B93" s="33"/>
-      <c r="C93" s="34" t="s">
+      <c r="A93" s="39"/>
+      <c r="B93" s="40"/>
+      <c r="C93" s="41" t="s">
         <v>221</v>
       </c>
-      <c r="D93" s="34" t="s">
+      <c r="D93" s="41" t="s">
         <v>222</v>
       </c>
-      <c r="E93" s="34" t="s">
+      <c r="E93" s="41" t="s">
         <v>223</v>
       </c>
-      <c r="F93" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G93" s="35"/>
-      <c r="H93" s="33"/>
-      <c r="I93" s="7"/>
+      <c r="F93" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93" s="42"/>
+      <c r="H93" s="43"/>
+      <c r="I93" s="8"/>
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="32"/>
-      <c r="B94" s="33"/>
-      <c r="C94" s="34" t="s">
+      <c r="A94" s="39"/>
+      <c r="B94" s="40"/>
+      <c r="C94" s="41" t="s">
         <v>224</v>
       </c>
-      <c r="D94" s="34" t="s">
+      <c r="D94" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="E94" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F94" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G94" s="35"/>
-      <c r="H94" s="33"/>
-      <c r="I94" s="7"/>
+      <c r="E94" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94" s="42"/>
+      <c r="H94" s="43"/>
+      <c r="I94" s="8"/>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="32"/>
-      <c r="B95" s="33"/>
-      <c r="C95" s="34" t="s">
+      <c r="A95" s="39"/>
+      <c r="B95" s="40"/>
+      <c r="C95" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="D95" s="34" t="s">
+      <c r="D95" s="41" t="s">
         <v>227</v>
       </c>
-      <c r="E95" s="34" t="s">
+      <c r="E95" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="F95" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G95" s="35"/>
-      <c r="H95" s="33"/>
-      <c r="I95" s="7"/>
+      <c r="F95" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G95" s="42"/>
+      <c r="H95" s="43"/>
+      <c r="I95" s="8"/>
     </row>
     <row r="96" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="20">
+      <c r="A96" s="24">
         <v>15</v>
       </c>
-      <c r="B96" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="C96" s="22" t="s">
+      <c r="B96" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="D96" s="22" t="s">
+      <c r="C96" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="E96" s="22" t="s">
+      <c r="D96" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="F96" s="22" t="s">
+      <c r="E96" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="G96" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="H96" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="I96" s="51" t="s">
-        <v>302</v>
+      <c r="F96" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="G96" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="H96" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="I96" s="62" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="20"/>
-      <c r="B97" s="21"/>
-      <c r="C97" s="22" t="s">
+      <c r="A97" s="24"/>
+      <c r="B97" s="25"/>
+      <c r="C97" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="D97" s="22" t="s">
+      <c r="D97" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="E97" s="22" t="s">
+      <c r="E97" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="F97" s="22" t="s">
+      <c r="F97" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="G97" s="23"/>
-      <c r="H97" s="21"/>
-      <c r="I97" s="51"/>
+      <c r="G97" s="27"/>
+      <c r="H97" s="28"/>
+      <c r="I97" s="62"/>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="20"/>
-      <c r="B98" s="21"/>
-      <c r="C98" s="22" t="s">
+      <c r="A98" s="24"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="D98" s="22" t="s">
+      <c r="D98" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="E98" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F98" s="22" t="s">
+      <c r="E98" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F98" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="G98" s="23"/>
-      <c r="H98" s="21"/>
-      <c r="I98" s="51"/>
+      <c r="G98" s="27"/>
+      <c r="H98" s="28"/>
+      <c r="I98" s="62"/>
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="20"/>
-      <c r="B99" s="21"/>
-      <c r="C99" s="22" t="s">
+      <c r="A99" s="24"/>
+      <c r="B99" s="25"/>
+      <c r="C99" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="D99" s="22" t="s">
+      <c r="D99" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="E99" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F99" s="22" t="s">
+      <c r="E99" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F99" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="G99" s="23"/>
-      <c r="H99" s="21"/>
-      <c r="I99" s="51"/>
+      <c r="G99" s="27"/>
+      <c r="H99" s="28"/>
+      <c r="I99" s="62"/>
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="20"/>
-      <c r="B100" s="21"/>
-      <c r="C100" s="22" t="s">
+      <c r="A100" s="24"/>
+      <c r="B100" s="25"/>
+      <c r="C100" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="D100" s="22" t="s">
+      <c r="D100" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="E100" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F100" s="22" t="s">
+      <c r="E100" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F100" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="G100" s="23"/>
-      <c r="H100" s="21"/>
-      <c r="I100" s="51"/>
+      <c r="G100" s="27"/>
+      <c r="H100" s="28"/>
+      <c r="I100" s="62"/>
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="20"/>
-      <c r="B101" s="21"/>
-      <c r="C101" s="22" t="s">
+      <c r="A101" s="24"/>
+      <c r="B101" s="25"/>
+      <c r="C101" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="D101" s="22" t="s">
+      <c r="D101" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="E101" s="22" t="s">
+      <c r="E101" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="F101" s="22" t="s">
+      <c r="F101" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="G101" s="23"/>
-      <c r="H101" s="21"/>
-      <c r="I101" s="51"/>
+      <c r="G101" s="27"/>
+      <c r="H101" s="28"/>
+      <c r="I101" s="62"/>
     </row>
     <row r="102" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="39">
+      <c r="A102" s="47">
         <v>18</v>
       </c>
-      <c r="B102" s="40" t="s">
-        <v>317</v>
-      </c>
-      <c r="C102" s="41" t="s">
-        <v>318</v>
-      </c>
-      <c r="D102" s="41" t="s">
+      <c r="B102" s="48" t="s">
         <v>319</v>
       </c>
-      <c r="E102" s="41" t="s">
+      <c r="C102" s="49" t="s">
         <v>320</v>
       </c>
-      <c r="F102" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="G102" s="42" t="s">
+      <c r="D102" s="49" t="s">
         <v>321</v>
       </c>
-      <c r="H102" s="40" t="s">
+      <c r="E102" s="49" t="s">
         <v>322</v>
       </c>
-      <c r="I102" s="51" t="s">
-        <v>302</v>
+      <c r="F102" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G102" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="H102" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="I102" s="62" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="39"/>
-      <c r="B103" s="40"/>
-      <c r="C103" s="41" t="s">
-        <v>323</v>
-      </c>
-      <c r="D103" s="41" t="s">
+      <c r="A103" s="47"/>
+      <c r="B103" s="48"/>
+      <c r="C103" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="E103" s="41" t="s">
+      <c r="D103" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="F103" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="G103" s="42"/>
-      <c r="H103" s="40"/>
-      <c r="I103" s="51"/>
+      <c r="E103" s="49" t="s">
+        <v>326</v>
+      </c>
+      <c r="F103" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" s="50"/>
+      <c r="H103" s="51"/>
+      <c r="I103" s="62"/>
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="39"/>
-      <c r="B104" s="40"/>
-      <c r="C104" s="41" t="s">
-        <v>326</v>
-      </c>
-      <c r="D104" s="41" t="s">
+      <c r="A104" s="47"/>
+      <c r="B104" s="48"/>
+      <c r="C104" s="49" t="s">
         <v>327</v>
       </c>
-      <c r="E104" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F104" s="41" t="s">
+      <c r="D104" s="49" t="s">
         <v>328</v>
       </c>
-      <c r="G104" s="42"/>
-      <c r="H104" s="40"/>
-      <c r="I104" s="51"/>
+      <c r="E104" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F104" s="49" t="s">
+        <v>329</v>
+      </c>
+      <c r="G104" s="50"/>
+      <c r="H104" s="51"/>
+      <c r="I104" s="62"/>
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="39"/>
-      <c r="B105" s="40"/>
-      <c r="C105" s="41" t="s">
-        <v>329</v>
-      </c>
-      <c r="D105" s="41" t="s">
+      <c r="A105" s="47"/>
+      <c r="B105" s="48"/>
+      <c r="C105" s="49" t="s">
         <v>330</v>
       </c>
-      <c r="E105" s="41" t="s">
+      <c r="D105" s="49" t="s">
         <v>331</v>
       </c>
-      <c r="F105" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="G105" s="42"/>
-      <c r="H105" s="40"/>
-      <c r="I105" s="51"/>
+      <c r="E105" s="49" t="s">
+        <v>332</v>
+      </c>
+      <c r="F105" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105" s="50"/>
+      <c r="H105" s="51"/>
+      <c r="I105" s="62"/>
     </row>
     <row r="106" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="39"/>
-      <c r="B106" s="40"/>
-      <c r="C106" s="41" t="s">
-        <v>332</v>
-      </c>
-      <c r="D106" s="41" t="s">
+      <c r="A106" s="47"/>
+      <c r="B106" s="48"/>
+      <c r="C106" s="49" t="s">
         <v>333</v>
       </c>
-      <c r="E106" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F106" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="G106" s="42"/>
-      <c r="H106" s="40"/>
-      <c r="I106" s="51"/>
+      <c r="D106" s="49" t="s">
+        <v>334</v>
+      </c>
+      <c r="E106" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F106" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G106" s="50"/>
+      <c r="H106" s="51"/>
+      <c r="I106" s="62"/>
     </row>
     <row r="107" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="52" t="s">
+      <c r="A107" s="63" t="s">
         <v>229</v>
       </c>
-      <c r="B107" s="52" t="s">
-        <v>334</v>
-      </c>
-      <c r="C107" s="52" t="s">
+      <c r="B107" s="63" t="s">
         <v>335</v>
       </c>
-      <c r="D107" s="52"/>
-      <c r="E107" s="52"/>
-      <c r="F107" s="52"/>
-      <c r="G107" s="52" t="s">
+      <c r="C107" s="63" t="s">
         <v>336</v>
       </c>
-      <c r="H107" s="53" t="s">
+      <c r="D107" s="63" t="s">
+        <v>229</v>
+      </c>
+      <c r="E107" s="63" t="s">
         <v>337</v>
       </c>
-      <c r="I107" s="52" t="s">
+      <c r="F107" s="63" t="s">
         <v>338</v>
       </c>
+      <c r="G107" s="63" t="s">
+        <v>339</v>
+      </c>
+      <c r="H107" s="64" t="s">
+        <v>340</v>
+      </c>
+      <c r="I107" s="63" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="109" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="54" t="s">
-        <v>339</v>
-      </c>
-      <c r="B109" s="54"/>
-      <c r="C109" s="54"/>
-      <c r="D109" s="54"/>
-      <c r="E109" s="54"/>
-      <c r="F109" s="54"/>
-      <c r="G109" s="54"/>
-      <c r="H109" s="54"/>
-      <c r="I109" s="54"/>
+      <c r="A109" s="65" t="s">
+        <v>342</v>
+      </c>
+      <c r="B109" s="65"/>
+      <c r="C109" s="65"/>
+      <c r="D109" s="65"/>
+      <c r="E109" s="65"/>
+      <c r="F109" s="65"/>
+      <c r="G109" s="65"/>
+      <c r="H109" s="65"/>
+      <c r="I109" s="65"/>
     </row>
     <row r="110" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="55">
+      <c r="A110" s="66">
         <v>8</v>
       </c>
-      <c r="B110" s="56" t="s">
-        <v>340</v>
-      </c>
-      <c r="C110" s="57" t="s">
-        <v>341</v>
-      </c>
-      <c r="D110" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="E110" s="57" t="s">
+      <c r="B110" s="67" t="s">
         <v>343</v>
       </c>
-      <c r="F110" s="57" t="s">
+      <c r="C110" s="68" t="s">
         <v>344</v>
       </c>
-      <c r="G110" s="58" t="s">
+      <c r="D110" s="68" t="s">
         <v>345</v>
       </c>
-      <c r="H110" s="56" t="s">
+      <c r="E110" s="68" t="s">
         <v>346</v>
       </c>
-      <c r="I110" s="7" t="s">
+      <c r="F110" s="68" t="s">
+        <v>347</v>
+      </c>
+      <c r="G110" s="69" t="s">
+        <v>348</v>
+      </c>
+      <c r="H110" s="70" t="s">
+        <v>94</v>
+      </c>
+      <c r="I110" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="55"/>
-      <c r="B111" s="56"/>
-      <c r="C111" s="57" t="s">
-        <v>347</v>
-      </c>
-      <c r="D111" s="57" t="s">
-        <v>348</v>
-      </c>
-      <c r="E111" s="57" t="s">
+      <c r="A111" s="66"/>
+      <c r="B111" s="67"/>
+      <c r="C111" s="68" t="s">
         <v>349</v>
       </c>
-      <c r="F111" s="57" t="s">
+      <c r="D111" s="68" t="s">
         <v>350</v>
       </c>
-      <c r="G111" s="58"/>
-      <c r="H111" s="56"/>
-      <c r="I111" s="7"/>
+      <c r="E111" s="68" t="s">
+        <v>351</v>
+      </c>
+      <c r="F111" s="68" t="s">
+        <v>352</v>
+      </c>
+      <c r="G111" s="69"/>
+      <c r="H111" s="70"/>
+      <c r="I111" s="8"/>
     </row>
     <row r="112" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="55"/>
-      <c r="B112" s="56"/>
-      <c r="C112" s="57" t="s">
-        <v>351</v>
-      </c>
-      <c r="D112" s="57" t="s">
-        <v>352</v>
-      </c>
-      <c r="E112" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="F112" s="57" t="s">
+      <c r="A112" s="66"/>
+      <c r="B112" s="67"/>
+      <c r="C112" s="68" t="s">
         <v>353</v>
       </c>
-      <c r="G112" s="58"/>
-      <c r="H112" s="56"/>
-      <c r="I112" s="7"/>
+      <c r="D112" s="68" t="s">
+        <v>354</v>
+      </c>
+      <c r="E112" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="F112" s="68" t="s">
+        <v>355</v>
+      </c>
+      <c r="G112" s="69"/>
+      <c r="H112" s="70"/>
+      <c r="I112" s="8"/>
     </row>
     <row r="113" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="55"/>
-      <c r="B113" s="56"/>
-      <c r="C113" s="57" t="s">
-        <v>354</v>
-      </c>
-      <c r="D113" s="57" t="s">
-        <v>355</v>
-      </c>
-      <c r="E113" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="F113" s="57" t="s">
+      <c r="A113" s="66"/>
+      <c r="B113" s="67"/>
+      <c r="C113" s="68" t="s">
         <v>356</v>
       </c>
-      <c r="G113" s="58"/>
-      <c r="H113" s="56"/>
-      <c r="I113" s="7"/>
+      <c r="D113" s="68" t="s">
+        <v>357</v>
+      </c>
+      <c r="E113" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="F113" s="68" t="s">
+        <v>358</v>
+      </c>
+      <c r="G113" s="69"/>
+      <c r="H113" s="70"/>
+      <c r="I113" s="8"/>
     </row>
     <row r="114" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="55"/>
-      <c r="B114" s="56"/>
-      <c r="C114" s="57" t="s">
-        <v>357</v>
-      </c>
-      <c r="D114" s="57" t="s">
-        <v>358</v>
-      </c>
-      <c r="E114" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="F114" s="57" t="s">
+      <c r="A114" s="66"/>
+      <c r="B114" s="67"/>
+      <c r="C114" s="68" t="s">
         <v>359</v>
       </c>
-      <c r="G114" s="58"/>
-      <c r="H114" s="56"/>
-      <c r="I114" s="7"/>
+      <c r="D114" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="E114" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="F114" s="68" t="s">
+        <v>361</v>
+      </c>
+      <c r="G114" s="69"/>
+      <c r="H114" s="70"/>
+      <c r="I114" s="8"/>
     </row>
     <row r="115" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="55"/>
-      <c r="B115" s="56"/>
-      <c r="C115" s="57" t="s">
-        <v>360</v>
-      </c>
-      <c r="D115" s="57" t="s">
-        <v>361</v>
-      </c>
-      <c r="E115" s="57" t="s">
+      <c r="A115" s="66"/>
+      <c r="B115" s="67"/>
+      <c r="C115" s="68" t="s">
         <v>362</v>
       </c>
-      <c r="F115" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G115" s="58"/>
-      <c r="H115" s="56"/>
-      <c r="I115" s="7"/>
+      <c r="D115" s="68" t="s">
+        <v>363</v>
+      </c>
+      <c r="E115" s="68" t="s">
+        <v>364</v>
+      </c>
+      <c r="F115" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G115" s="69"/>
+      <c r="H115" s="70"/>
+      <c r="I115" s="8"/>
     </row>
     <row r="116" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="59">
+      <c r="A116" s="71">
         <v>10</v>
       </c>
-      <c r="B116" s="60" t="s">
-        <v>363</v>
-      </c>
-      <c r="C116" s="61" t="s">
-        <v>364</v>
-      </c>
-      <c r="D116" s="61" t="s">
+      <c r="B116" s="72" t="s">
         <v>365</v>
       </c>
-      <c r="E116" s="61" t="s">
+      <c r="C116" s="73" t="s">
         <v>366</v>
       </c>
-      <c r="F116" s="61" t="s">
+      <c r="D116" s="73" t="s">
         <v>367</v>
       </c>
-      <c r="G116" s="62" t="s">
+      <c r="E116" s="73" t="s">
         <v>368</v>
       </c>
-      <c r="H116" s="60" t="s">
+      <c r="F116" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="I116" s="51" t="s">
-        <v>302</v>
+      <c r="G116" s="74" t="s">
+        <v>370</v>
+      </c>
+      <c r="H116" s="75" t="s">
+        <v>117</v>
+      </c>
+      <c r="I116" s="62" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="59"/>
-      <c r="B117" s="60"/>
-      <c r="C117" s="61" t="s">
-        <v>370</v>
-      </c>
-      <c r="D117" s="61" t="s">
+      <c r="A117" s="71"/>
+      <c r="B117" s="72"/>
+      <c r="C117" s="73" t="s">
         <v>371</v>
       </c>
-      <c r="E117" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="F117" s="61" t="s">
+      <c r="D117" s="73" t="s">
         <v>372</v>
       </c>
-      <c r="G117" s="62"/>
-      <c r="H117" s="60"/>
-      <c r="I117" s="51"/>
+      <c r="E117" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F117" s="73" t="s">
+        <v>373</v>
+      </c>
+      <c r="G117" s="74"/>
+      <c r="H117" s="75"/>
+      <c r="I117" s="62"/>
     </row>
     <row r="118" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="59"/>
-      <c r="B118" s="60"/>
-      <c r="C118" s="61" t="s">
-        <v>373</v>
-      </c>
-      <c r="D118" s="61" t="s">
+      <c r="A118" s="71"/>
+      <c r="B118" s="72"/>
+      <c r="C118" s="73" t="s">
         <v>374</v>
       </c>
-      <c r="E118" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="F118" s="61" t="s">
+      <c r="D118" s="73" t="s">
         <v>375</v>
       </c>
-      <c r="G118" s="62"/>
-      <c r="H118" s="60"/>
-      <c r="I118" s="51"/>
+      <c r="E118" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F118" s="73" t="s">
+        <v>376</v>
+      </c>
+      <c r="G118" s="74"/>
+      <c r="H118" s="75"/>
+      <c r="I118" s="62"/>
     </row>
     <row r="119" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="59"/>
-      <c r="B119" s="60"/>
-      <c r="C119" s="61" t="s">
-        <v>376</v>
-      </c>
-      <c r="D119" s="61" t="s">
+      <c r="A119" s="71"/>
+      <c r="B119" s="72"/>
+      <c r="C119" s="73" t="s">
         <v>377</v>
       </c>
-      <c r="E119" s="61" t="s">
+      <c r="D119" s="73" t="s">
         <v>378</v>
       </c>
-      <c r="F119" s="61" t="s">
+      <c r="E119" s="73" t="s">
         <v>379</v>
       </c>
-      <c r="G119" s="62"/>
-      <c r="H119" s="60"/>
-      <c r="I119" s="51"/>
+      <c r="F119" s="73" t="s">
+        <v>380</v>
+      </c>
+      <c r="G119" s="74"/>
+      <c r="H119" s="75"/>
+      <c r="I119" s="62"/>
     </row>
     <row r="120" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="59"/>
-      <c r="B120" s="60"/>
-      <c r="C120" s="61" t="s">
-        <v>380</v>
-      </c>
-      <c r="D120" s="61" t="s">
+      <c r="A120" s="71"/>
+      <c r="B120" s="72"/>
+      <c r="C120" s="73" t="s">
         <v>381</v>
       </c>
-      <c r="E120" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="F120" s="61" t="s">
+      <c r="D120" s="73" t="s">
         <v>382</v>
       </c>
-      <c r="G120" s="62"/>
-      <c r="H120" s="60"/>
-      <c r="I120" s="51"/>
+      <c r="E120" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F120" s="73" t="s">
+        <v>383</v>
+      </c>
+      <c r="G120" s="74"/>
+      <c r="H120" s="75"/>
+      <c r="I120" s="62"/>
     </row>
     <row r="121" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="59"/>
-      <c r="B121" s="60"/>
-      <c r="C121" s="61" t="s">
-        <v>383</v>
-      </c>
-      <c r="D121" s="61" t="s">
+      <c r="A121" s="71"/>
+      <c r="B121" s="72"/>
+      <c r="C121" s="73" t="s">
         <v>384</v>
       </c>
-      <c r="E121" s="61" t="s">
+      <c r="D121" s="73" t="s">
         <v>385</v>
       </c>
-      <c r="F121" s="61" t="s">
+      <c r="E121" s="73" t="s">
         <v>386</v>
       </c>
-      <c r="G121" s="62"/>
-      <c r="H121" s="60"/>
-      <c r="I121" s="51"/>
+      <c r="F121" s="73" t="s">
+        <v>387</v>
+      </c>
+      <c r="G121" s="74"/>
+      <c r="H121" s="75"/>
+      <c r="I121" s="62"/>
     </row>
     <row r="122" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="39">
+      <c r="A122" s="47">
         <v>4</v>
       </c>
-      <c r="B122" s="40" t="s">
-        <v>249</v>
-      </c>
-      <c r="C122" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="D122" s="41" t="s">
+      <c r="B122" s="48" t="s">
         <v>251</v>
       </c>
-      <c r="E122" s="41" t="s">
+      <c r="C122" s="49" t="s">
         <v>252</v>
       </c>
-      <c r="F122" s="41" t="s">
+      <c r="D122" s="49" t="s">
         <v>253</v>
       </c>
-      <c r="G122" s="42" t="s">
-        <v>387</v>
-      </c>
-      <c r="H122" s="40" t="s">
+      <c r="E122" s="49" t="s">
+        <v>254</v>
+      </c>
+      <c r="F122" s="49" t="s">
+        <v>255</v>
+      </c>
+      <c r="G122" s="50" t="s">
         <v>388</v>
       </c>
-      <c r="I122" s="51" t="s">
-        <v>302</v>
+      <c r="H122" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="I122" s="62" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="39"/>
-      <c r="B123" s="40"/>
-      <c r="C123" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="D123" s="41" t="s">
-        <v>257</v>
-      </c>
-      <c r="E123" s="41" t="s">
+      <c r="A123" s="47"/>
+      <c r="B123" s="48"/>
+      <c r="C123" s="49" t="s">
         <v>258</v>
       </c>
-      <c r="F123" s="41" t="s">
+      <c r="D123" s="49" t="s">
         <v>259</v>
       </c>
-      <c r="G123" s="42"/>
-      <c r="H123" s="40"/>
-      <c r="I123" s="51"/>
+      <c r="E123" s="49" t="s">
+        <v>260</v>
+      </c>
+      <c r="F123" s="49" t="s">
+        <v>261</v>
+      </c>
+      <c r="G123" s="50"/>
+      <c r="H123" s="51"/>
+      <c r="I123" s="62"/>
     </row>
     <row r="124" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="39"/>
-      <c r="B124" s="40"/>
-      <c r="C124" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="D124" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="E124" s="41" t="s">
+      <c r="A124" s="47"/>
+      <c r="B124" s="48"/>
+      <c r="C124" s="49" t="s">
         <v>262</v>
       </c>
-      <c r="F124" s="41" t="s">
+      <c r="D124" s="49" t="s">
         <v>263</v>
       </c>
-      <c r="G124" s="42"/>
-      <c r="H124" s="40"/>
-      <c r="I124" s="51"/>
+      <c r="E124" s="49" t="s">
+        <v>264</v>
+      </c>
+      <c r="F124" s="49" t="s">
+        <v>265</v>
+      </c>
+      <c r="G124" s="50"/>
+      <c r="H124" s="51"/>
+      <c r="I124" s="62"/>
     </row>
     <row r="125" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="39"/>
-      <c r="B125" s="40"/>
-      <c r="C125" s="41" t="s">
-        <v>264</v>
-      </c>
-      <c r="D125" s="41" t="s">
-        <v>265</v>
-      </c>
-      <c r="E125" s="41" t="s">
+      <c r="A125" s="47"/>
+      <c r="B125" s="48"/>
+      <c r="C125" s="49" t="s">
         <v>266</v>
       </c>
-      <c r="F125" s="41" t="s">
+      <c r="D125" s="49" t="s">
         <v>267</v>
       </c>
-      <c r="G125" s="42"/>
-      <c r="H125" s="40"/>
-      <c r="I125" s="51"/>
+      <c r="E125" s="49" t="s">
+        <v>268</v>
+      </c>
+      <c r="F125" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="G125" s="50"/>
+      <c r="H125" s="51"/>
+      <c r="I125" s="62"/>
     </row>
     <row r="126" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="39"/>
-      <c r="B126" s="40"/>
-      <c r="C126" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="D126" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="E126" s="41" t="s">
+      <c r="A126" s="47"/>
+      <c r="B126" s="48"/>
+      <c r="C126" s="49" t="s">
+        <v>270</v>
+      </c>
+      <c r="D126" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="E126" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="F126" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="G126" s="42"/>
-      <c r="H126" s="40"/>
-      <c r="I126" s="51"/>
+      <c r="F126" s="49" t="s">
+        <v>272</v>
+      </c>
+      <c r="G126" s="50"/>
+      <c r="H126" s="51"/>
+      <c r="I126" s="62"/>
     </row>
     <row r="127" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="39"/>
-      <c r="B127" s="40"/>
-      <c r="C127" s="41" t="s">
-        <v>271</v>
-      </c>
-      <c r="D127" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="E127" s="41" t="s">
+      <c r="A127" s="47"/>
+      <c r="B127" s="48"/>
+      <c r="C127" s="49" t="s">
         <v>273</v>
       </c>
-      <c r="F127" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="G127" s="42"/>
-      <c r="H127" s="40"/>
-      <c r="I127" s="51"/>
+      <c r="D127" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="E127" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="F127" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" s="50"/>
+      <c r="H127" s="51"/>
+      <c r="I127" s="62"/>
     </row>
     <row r="128" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="39"/>
-      <c r="B128" s="40"/>
-      <c r="C128" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="D128" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="E128" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F128" s="41" t="s">
+      <c r="A128" s="47"/>
+      <c r="B128" s="48"/>
+      <c r="C128" s="49" t="s">
         <v>276</v>
       </c>
-      <c r="G128" s="42"/>
-      <c r="H128" s="40"/>
-      <c r="I128" s="51"/>
+      <c r="D128" s="49" t="s">
+        <v>277</v>
+      </c>
+      <c r="E128" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F128" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="G128" s="50"/>
+      <c r="H128" s="51"/>
+      <c r="I128" s="62"/>
     </row>
     <row r="129" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="39"/>
-      <c r="B129" s="40"/>
-      <c r="C129" s="41" t="s">
-        <v>277</v>
-      </c>
-      <c r="D129" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="E129" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F129" s="41" t="s">
+      <c r="A129" s="47"/>
+      <c r="B129" s="48"/>
+      <c r="C129" s="49" t="s">
         <v>279</v>
       </c>
-      <c r="G129" s="42"/>
-      <c r="H129" s="40"/>
-      <c r="I129" s="51"/>
+      <c r="D129" s="49" t="s">
+        <v>280</v>
+      </c>
+      <c r="E129" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F129" s="49" t="s">
+        <v>281</v>
+      </c>
+      <c r="G129" s="50"/>
+      <c r="H129" s="51"/>
+      <c r="I129" s="62"/>
     </row>
     <row r="130" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="63">
+      <c r="A130" s="76">
         <v>12</v>
       </c>
-      <c r="B130" s="64" t="s">
+      <c r="B130" s="77" t="s">
         <v>389</v>
       </c>
-      <c r="C130" s="65" t="s">
+      <c r="C130" s="78" t="s">
         <v>390</v>
       </c>
-      <c r="D130" s="65" t="s">
+      <c r="D130" s="78" t="s">
         <v>391</v>
       </c>
-      <c r="E130" s="65" t="s">
+      <c r="E130" s="78" t="s">
         <v>392</v>
       </c>
-      <c r="F130" s="65" t="s">
+      <c r="F130" s="78" t="s">
         <v>393</v>
       </c>
-      <c r="G130" s="66" t="s">
+      <c r="G130" s="79" t="s">
         <v>394</v>
       </c>
-      <c r="H130" s="64" t="s">
-        <v>322</v>
-      </c>
-      <c r="I130" s="7" t="s">
+      <c r="H130" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="I130" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="131" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="63"/>
-      <c r="B131" s="64"/>
-      <c r="C131" s="65" t="s">
+      <c r="A131" s="76"/>
+      <c r="B131" s="77"/>
+      <c r="C131" s="78" t="s">
         <v>395</v>
       </c>
-      <c r="D131" s="65" t="s">
+      <c r="D131" s="78" t="s">
         <v>396</v>
       </c>
-      <c r="E131" s="65" t="s">
+      <c r="E131" s="78" t="s">
         <v>397</v>
       </c>
-      <c r="F131" s="65" t="s">
+      <c r="F131" s="78" t="s">
         <v>398</v>
       </c>
-      <c r="G131" s="66"/>
-      <c r="H131" s="64"/>
-      <c r="I131" s="7"/>
+      <c r="G131" s="79"/>
+      <c r="H131" s="80"/>
+      <c r="I131" s="8"/>
     </row>
     <row r="132" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="63"/>
-      <c r="B132" s="64"/>
-      <c r="C132" s="65" t="s">
+      <c r="A132" s="76"/>
+      <c r="B132" s="77"/>
+      <c r="C132" s="78" t="s">
         <v>399</v>
       </c>
-      <c r="D132" s="65" t="s">
+      <c r="D132" s="78" t="s">
         <v>400</v>
       </c>
-      <c r="E132" s="65" t="s">
+      <c r="E132" s="78" t="s">
         <v>401</v>
       </c>
-      <c r="F132" s="65" t="s">
+      <c r="F132" s="78" t="s">
         <v>402</v>
       </c>
-      <c r="G132" s="66"/>
-      <c r="H132" s="64"/>
-      <c r="I132" s="7"/>
+      <c r="G132" s="79"/>
+      <c r="H132" s="80"/>
+      <c r="I132" s="8"/>
     </row>
     <row r="133" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="63"/>
-      <c r="B133" s="64"/>
-      <c r="C133" s="65" t="s">
+      <c r="A133" s="76"/>
+      <c r="B133" s="77"/>
+      <c r="C133" s="78" t="s">
         <v>403</v>
       </c>
-      <c r="D133" s="65" t="s">
+      <c r="D133" s="78" t="s">
         <v>404</v>
       </c>
-      <c r="E133" s="65" t="s">
-        <v>14</v>
-      </c>
-      <c r="F133" s="65" t="s">
+      <c r="E133" s="78" t="s">
+        <v>14</v>
+      </c>
+      <c r="F133" s="78" t="s">
         <v>405</v>
       </c>
-      <c r="G133" s="66"/>
-      <c r="H133" s="64"/>
-      <c r="I133" s="7"/>
+      <c r="G133" s="79"/>
+      <c r="H133" s="80"/>
+      <c r="I133" s="8"/>
     </row>
     <row r="134" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="63"/>
-      <c r="B134" s="64"/>
-      <c r="C134" s="65" t="s">
+      <c r="A134" s="76"/>
+      <c r="B134" s="77"/>
+      <c r="C134" s="78" t="s">
         <v>406</v>
       </c>
-      <c r="D134" s="65" t="s">
+      <c r="D134" s="78" t="s">
         <v>407</v>
       </c>
-      <c r="E134" s="65" t="s">
+      <c r="E134" s="78" t="s">
         <v>408</v>
       </c>
-      <c r="F134" s="65" t="s">
+      <c r="F134" s="78" t="s">
         <v>409</v>
       </c>
-      <c r="G134" s="66"/>
-      <c r="H134" s="64"/>
-      <c r="I134" s="7"/>
+      <c r="G134" s="79"/>
+      <c r="H134" s="80"/>
+      <c r="I134" s="8"/>
     </row>
     <row r="135" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
@@ -5546,11 +5833,11 @@
       <c r="G135" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="H135" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="I135" s="51" t="s">
-        <v>302</v>
+      <c r="H135" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="I135" s="62" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="136" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5569,8 +5856,8 @@
         <v>21</v>
       </c>
       <c r="G136" s="6"/>
-      <c r="H136" s="4"/>
-      <c r="I136" s="51"/>
+      <c r="H136" s="7"/>
+      <c r="I136" s="62"/>
     </row>
     <row r="137" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="3"/>
@@ -5588,8 +5875,8 @@
         <v>25</v>
       </c>
       <c r="G137" s="6"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="51"/>
+      <c r="H137" s="7"/>
+      <c r="I137" s="62"/>
     </row>
     <row r="138" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="3"/>
@@ -5607,8 +5894,8 @@
         <v>14</v>
       </c>
       <c r="G138" s="6"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="51"/>
+      <c r="H138" s="7"/>
+      <c r="I138" s="62"/>
     </row>
     <row r="139" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="3"/>
@@ -5626,8 +5913,8 @@
         <v>14</v>
       </c>
       <c r="G139" s="6"/>
-      <c r="H139" s="4"/>
-      <c r="I139" s="51"/>
+      <c r="H139" s="7"/>
+      <c r="I139" s="62"/>
     </row>
     <row r="140" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="3"/>
@@ -5645,477 +5932,903 @@
         <v>35</v>
       </c>
       <c r="G140" s="6"/>
-      <c r="H140" s="4"/>
-      <c r="I140" s="51"/>
+      <c r="H140" s="7"/>
+      <c r="I140" s="62"/>
     </row>
     <row r="141" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="67">
+      <c r="A141" s="81">
         <v>17</v>
       </c>
-      <c r="B141" s="68" t="s">
+      <c r="B141" s="82" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="83" t="s">
         <v>412</v>
       </c>
-      <c r="C141" s="69" t="s">
+      <c r="D141" s="83" t="s">
         <v>413</v>
       </c>
-      <c r="D141" s="69" t="s">
+      <c r="E141" s="83" t="s">
         <v>414</v>
       </c>
-      <c r="E141" s="69" t="s">
+      <c r="F141" s="83" t="s">
         <v>415</v>
       </c>
-      <c r="F141" s="69" t="s">
+      <c r="G141" s="84" t="s">
         <v>416</v>
       </c>
-      <c r="G141" s="70" t="s">
+      <c r="H141" s="85" t="s">
+        <v>16</v>
+      </c>
+      <c r="I141" s="62" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="81"/>
+      <c r="B142" s="82"/>
+      <c r="C142" s="83" t="s">
         <v>417</v>
       </c>
-      <c r="H141" s="68" t="s">
+      <c r="D142" s="83" t="s">
         <v>418</v>
       </c>
-      <c r="I141" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="142" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="67"/>
-      <c r="B142" s="68"/>
-      <c r="C142" s="69" t="s">
+      <c r="E142" s="83" t="s">
+        <v>14</v>
+      </c>
+      <c r="F142" s="83" t="s">
         <v>419</v>
       </c>
-      <c r="D142" s="69" t="s">
+      <c r="G142" s="84"/>
+      <c r="H142" s="85"/>
+      <c r="I142" s="62"/>
+    </row>
+    <row r="143" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="81"/>
+      <c r="B143" s="82"/>
+      <c r="C143" s="83" t="s">
         <v>420</v>
       </c>
-      <c r="E142" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="F142" s="69" t="s">
+      <c r="D143" s="83" t="s">
         <v>421</v>
       </c>
-      <c r="G142" s="70"/>
-      <c r="H142" s="68"/>
-      <c r="I142" s="51"/>
-    </row>
-    <row r="143" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="67"/>
-      <c r="B143" s="68"/>
-      <c r="C143" s="69" t="s">
+      <c r="E143" s="83" t="s">
         <v>422</v>
       </c>
-      <c r="D143" s="69" t="s">
+      <c r="F143" s="83" t="s">
         <v>423</v>
       </c>
-      <c r="E143" s="69" t="s">
+      <c r="G143" s="84"/>
+      <c r="H143" s="85"/>
+      <c r="I143" s="62"/>
+    </row>
+    <row r="144" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="81"/>
+      <c r="B144" s="82"/>
+      <c r="C144" s="83" t="s">
         <v>424</v>
       </c>
-      <c r="F143" s="69" t="s">
+      <c r="D144" s="83" t="s">
         <v>425</v>
       </c>
-      <c r="G143" s="70"/>
-      <c r="H143" s="68"/>
-      <c r="I143" s="51"/>
-    </row>
-    <row r="144" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="67"/>
-      <c r="B144" s="68"/>
-      <c r="C144" s="69" t="s">
+      <c r="E144" s="83" t="s">
         <v>426</v>
       </c>
-      <c r="D144" s="69" t="s">
+      <c r="F144" s="83" t="s">
         <v>427</v>
       </c>
-      <c r="E144" s="69" t="s">
+      <c r="G144" s="84"/>
+      <c r="H144" s="85"/>
+      <c r="I144" s="62"/>
+    </row>
+    <row r="145" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="24">
+        <v>15</v>
+      </c>
+      <c r="B145" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="C145" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="D145" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="E145" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="F145" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="G145" s="27" t="s">
         <v>428</v>
       </c>
-      <c r="F144" s="69" t="s">
+      <c r="H145" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="I145" s="62" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="146" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="24"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="D146" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="E146" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="F146" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="G146" s="27"/>
+      <c r="H146" s="28"/>
+      <c r="I146" s="62"/>
+    </row>
+    <row r="147" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="24"/>
+      <c r="B147" s="25"/>
+      <c r="C147" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="D147" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="E147" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F147" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="G147" s="27"/>
+      <c r="H147" s="28"/>
+      <c r="I147" s="62"/>
+    </row>
+    <row r="148" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="24"/>
+      <c r="B148" s="25"/>
+      <c r="C148" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="D148" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E148" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F148" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="G148" s="27"/>
+      <c r="H148" s="28"/>
+      <c r="I148" s="62"/>
+    </row>
+    <row r="149" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="24"/>
+      <c r="B149" s="25"/>
+      <c r="C149" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="D149" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="E149" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F149" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="G149" s="27"/>
+      <c r="H149" s="28"/>
+      <c r="I149" s="62"/>
+    </row>
+    <row r="150" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="24"/>
+      <c r="B150" s="25"/>
+      <c r="C150" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="D150" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="E150" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="F150" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="G150" s="27"/>
+      <c r="H150" s="28"/>
+      <c r="I150" s="62"/>
+    </row>
+    <row r="151" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="39">
+        <v>1</v>
+      </c>
+      <c r="B151" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="C151" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="D151" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="E151" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="F151" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="G151" s="42" t="s">
         <v>429</v>
       </c>
-      <c r="G144" s="70"/>
-      <c r="H144" s="68"/>
-      <c r="I144" s="51"/>
-    </row>
-    <row r="145" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="20">
-        <v>15</v>
-      </c>
-      <c r="B145" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="C145" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="D145" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="E145" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="F145" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="G145" s="23" t="s">
+      <c r="H151" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="I151" s="62" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="152" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="39"/>
+      <c r="B152" s="40"/>
+      <c r="C152" s="41" t="s">
+        <v>221</v>
+      </c>
+      <c r="D152" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="E152" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="F152" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G152" s="42"/>
+      <c r="H152" s="43"/>
+      <c r="I152" s="62"/>
+    </row>
+    <row r="153" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="39"/>
+      <c r="B153" s="40"/>
+      <c r="C153" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="D153" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="E153" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="F153" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G153" s="42"/>
+      <c r="H153" s="43"/>
+      <c r="I153" s="62"/>
+    </row>
+    <row r="154" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="39"/>
+      <c r="B154" s="40"/>
+      <c r="C154" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="D154" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="E154" s="41" t="s">
+        <v>228</v>
+      </c>
+      <c r="F154" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G154" s="42"/>
+      <c r="H154" s="43"/>
+      <c r="I154" s="62"/>
+    </row>
+    <row r="155" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="86">
+        <v>20</v>
+      </c>
+      <c r="B155" s="87" t="s">
         <v>430</v>
       </c>
-      <c r="H145" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="I145" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="146" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="20"/>
-      <c r="B146" s="21"/>
-      <c r="C146" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="D146" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="E146" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="F146" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="G146" s="23"/>
-      <c r="H146" s="21"/>
-      <c r="I146" s="51"/>
-    </row>
-    <row r="147" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="20"/>
-      <c r="B147" s="21"/>
-      <c r="C147" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="D147" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="E147" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F147" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="G147" s="23"/>
-      <c r="H147" s="21"/>
-      <c r="I147" s="51"/>
-    </row>
-    <row r="148" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="20"/>
-      <c r="B148" s="21"/>
-      <c r="C148" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="D148" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="E148" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F148" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="G148" s="23"/>
-      <c r="H148" s="21"/>
-      <c r="I148" s="51"/>
-    </row>
-    <row r="149" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="20"/>
-      <c r="B149" s="21"/>
-      <c r="C149" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="D149" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="E149" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F149" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="G149" s="23"/>
-      <c r="H149" s="21"/>
-      <c r="I149" s="51"/>
-    </row>
-    <row r="150" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="20"/>
-      <c r="B150" s="21"/>
-      <c r="C150" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="D150" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="E150" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="F150" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="G150" s="23"/>
-      <c r="H150" s="21"/>
-      <c r="I150" s="51"/>
-    </row>
-    <row r="151" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="32">
+      <c r="C155" s="88" t="s">
+        <v>431</v>
+      </c>
+      <c r="D155" s="88" t="s">
+        <v>432</v>
+      </c>
+      <c r="E155" s="88" t="s">
+        <v>14</v>
+      </c>
+      <c r="F155" s="88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G155" s="89" t="s">
+        <v>433</v>
+      </c>
+      <c r="H155" s="90" t="s">
+        <v>434</v>
+      </c>
+      <c r="I155" s="62" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="156" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="86"/>
+      <c r="B156" s="87"/>
+      <c r="C156" s="88" t="s">
+        <v>435</v>
+      </c>
+      <c r="D156" s="88" t="s">
+        <v>436</v>
+      </c>
+      <c r="E156" s="88" t="s">
+        <v>14</v>
+      </c>
+      <c r="F156" s="88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G156" s="89"/>
+      <c r="H156" s="90"/>
+      <c r="I156" s="62"/>
+    </row>
+    <row r="157" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="86"/>
+      <c r="B157" s="87"/>
+      <c r="C157" s="88" t="s">
+        <v>437</v>
+      </c>
+      <c r="D157" s="88" t="s">
+        <v>438</v>
+      </c>
+      <c r="E157" s="88" t="s">
+        <v>14</v>
+      </c>
+      <c r="F157" s="88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G157" s="89"/>
+      <c r="H157" s="90"/>
+      <c r="I157" s="62"/>
+    </row>
+    <row r="158" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="86"/>
+      <c r="B158" s="87"/>
+      <c r="C158" s="88" t="s">
+        <v>439</v>
+      </c>
+      <c r="D158" s="88" t="s">
+        <v>440</v>
+      </c>
+      <c r="E158" s="88" t="s">
+        <v>441</v>
+      </c>
+      <c r="F158" s="88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G158" s="89"/>
+      <c r="H158" s="90"/>
+      <c r="I158" s="62"/>
+    </row>
+    <row r="159" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="86"/>
+      <c r="B159" s="87"/>
+      <c r="C159" s="88" t="s">
+        <v>442</v>
+      </c>
+      <c r="D159" s="88" t="s">
+        <v>443</v>
+      </c>
+      <c r="E159" s="88" t="s">
+        <v>444</v>
+      </c>
+      <c r="F159" s="88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G159" s="89"/>
+      <c r="H159" s="90"/>
+      <c r="I159" s="62"/>
+    </row>
+    <row r="160" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="86"/>
+      <c r="B160" s="87"/>
+      <c r="C160" s="88" t="s">
+        <v>445</v>
+      </c>
+      <c r="D160" s="88" t="s">
+        <v>446</v>
+      </c>
+      <c r="E160" s="88" t="s">
+        <v>228</v>
+      </c>
+      <c r="F160" s="88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G160" s="89"/>
+      <c r="H160" s="90"/>
+      <c r="I160" s="62"/>
+    </row>
+    <row r="161" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="91" t="s">
+        <v>229</v>
+      </c>
+      <c r="B161" s="91" t="s">
+        <v>447</v>
+      </c>
+      <c r="C161" s="91" t="s">
+        <v>448</v>
+      </c>
+      <c r="D161" s="91" t="s">
+        <v>229</v>
+      </c>
+      <c r="E161" s="91" t="s">
+        <v>449</v>
+      </c>
+      <c r="F161" s="91" t="s">
+        <v>450</v>
+      </c>
+      <c r="G161" s="91" t="s">
+        <v>451</v>
+      </c>
+      <c r="H161" s="92" t="s">
+        <v>452</v>
+      </c>
+      <c r="I161" s="91" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="162" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="H162" s="93" t="s">
+        <v>458</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="164" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="94" t="s">
+        <v>229</v>
+      </c>
+      <c r="B164" s="94"/>
+      <c r="C164" s="94"/>
+      <c r="D164" s="94"/>
+      <c r="E164" s="94"/>
+      <c r="F164" s="94"/>
+      <c r="G164" s="94"/>
+      <c r="H164" s="94"/>
+      <c r="I164" s="94"/>
+    </row>
+    <row r="165" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="95" t="s">
+        <v>0</v>
+      </c>
+      <c r="B165" s="95" t="s">
+        <v>229</v>
+      </c>
+      <c r="C165" s="95" t="s">
+        <v>459</v>
+      </c>
+      <c r="D165" s="95"/>
+      <c r="E165" s="95"/>
+      <c r="F165" s="95" t="s">
+        <v>460</v>
+      </c>
+      <c r="G165" s="95" t="s">
+        <v>229</v>
+      </c>
+      <c r="H165" s="95" t="s">
+        <v>461</v>
+      </c>
+      <c r="I165" s="95" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="96">
         <v>1</v>
       </c>
-      <c r="B151" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="C151" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="D151" s="34" t="s">
-        <v>216</v>
-      </c>
-      <c r="E151" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="F151" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="G151" s="35" t="s">
-        <v>431</v>
-      </c>
-      <c r="H151" s="33" t="s">
-        <v>315</v>
-      </c>
-      <c r="I151" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="152" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="32"/>
-      <c r="B152" s="33"/>
-      <c r="C152" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="D152" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="E152" s="34" t="s">
-        <v>223</v>
-      </c>
-      <c r="F152" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G152" s="35"/>
-      <c r="H152" s="33"/>
-      <c r="I152" s="51"/>
-    </row>
-    <row r="153" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="32"/>
-      <c r="B153" s="33"/>
-      <c r="C153" s="34" t="s">
-        <v>224</v>
-      </c>
-      <c r="D153" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="E153" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F153" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G153" s="35"/>
-      <c r="H153" s="33"/>
-      <c r="I153" s="51"/>
-    </row>
-    <row r="154" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="32"/>
-      <c r="B154" s="33"/>
-      <c r="C154" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="D154" s="34" t="s">
-        <v>227</v>
-      </c>
-      <c r="E154" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="F154" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G154" s="35"/>
-      <c r="H154" s="33"/>
-      <c r="I154" s="51"/>
-    </row>
-    <row r="155" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="71">
-        <v>20</v>
-      </c>
-      <c r="B155" s="72" t="s">
-        <v>432</v>
-      </c>
-      <c r="C155" s="73" t="s">
-        <v>433</v>
-      </c>
-      <c r="D155" s="73" t="s">
-        <v>434</v>
-      </c>
-      <c r="E155" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="F155" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="G155" s="74" t="s">
-        <v>435</v>
-      </c>
-      <c r="H155" s="72" t="s">
-        <v>436</v>
-      </c>
-      <c r="I155" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="156" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="71"/>
-      <c r="B156" s="72"/>
-      <c r="C156" s="73" t="s">
-        <v>437</v>
-      </c>
-      <c r="D156" s="73" t="s">
-        <v>438</v>
-      </c>
-      <c r="E156" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="F156" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="G156" s="74"/>
-      <c r="H156" s="72"/>
-      <c r="I156" s="51"/>
-    </row>
-    <row r="157" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="71"/>
-      <c r="B157" s="72"/>
-      <c r="C157" s="73" t="s">
-        <v>439</v>
-      </c>
-      <c r="D157" s="73" t="s">
-        <v>440</v>
-      </c>
-      <c r="E157" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="F157" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="G157" s="74"/>
-      <c r="H157" s="72"/>
-      <c r="I157" s="51"/>
-    </row>
-    <row r="158" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="71"/>
-      <c r="B158" s="72"/>
-      <c r="C158" s="73" t="s">
-        <v>441</v>
-      </c>
-      <c r="D158" s="73" t="s">
-        <v>442</v>
-      </c>
-      <c r="E158" s="73" t="s">
-        <v>443</v>
-      </c>
-      <c r="F158" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="G158" s="74"/>
-      <c r="H158" s="72"/>
-      <c r="I158" s="51"/>
-    </row>
-    <row r="159" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="71"/>
-      <c r="B159" s="72"/>
-      <c r="C159" s="73" t="s">
-        <v>444</v>
-      </c>
-      <c r="D159" s="73" t="s">
-        <v>445</v>
-      </c>
-      <c r="E159" s="73" t="s">
-        <v>446</v>
-      </c>
-      <c r="F159" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="G159" s="74"/>
-      <c r="H159" s="72"/>
-      <c r="I159" s="51"/>
-    </row>
-    <row r="160" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" s="71"/>
-      <c r="B160" s="72"/>
-      <c r="C160" s="73" t="s">
-        <v>447</v>
-      </c>
-      <c r="D160" s="73" t="s">
-        <v>448</v>
-      </c>
-      <c r="E160" s="73" t="s">
-        <v>228</v>
-      </c>
-      <c r="F160" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="G160" s="74"/>
-      <c r="H160" s="72"/>
-      <c r="I160" s="51"/>
-    </row>
-    <row r="161" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" s="75" t="s">
+      <c r="B166" s="96" t="s">
         <v>229</v>
       </c>
-      <c r="B161" s="75" t="s">
-        <v>449</v>
-      </c>
-      <c r="C161" s="75" t="s">
-        <v>450</v>
-      </c>
-      <c r="D161" s="75"/>
-      <c r="E161" s="75"/>
-      <c r="F161" s="75"/>
-      <c r="G161" s="75" t="s">
-        <v>451</v>
-      </c>
-      <c r="H161" s="76" t="s">
-        <v>452</v>
-      </c>
-      <c r="I161" s="75" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="162" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162" s="77" t="s">
+      <c r="C166" s="97" t="s">
+        <v>462</v>
+      </c>
+      <c r="D166" s="97"/>
+      <c r="E166" s="97"/>
+      <c r="F166" s="96" t="s">
+        <v>463</v>
+      </c>
+      <c r="G166" s="96" t="s">
         <v>229</v>
       </c>
-      <c r="B162" s="77" t="s">
-        <v>454</v>
-      </c>
-      <c r="C162" s="77" t="s">
-        <v>455</v>
-      </c>
-      <c r="D162" s="77"/>
-      <c r="E162" s="77"/>
-      <c r="F162" s="77"/>
-      <c r="G162" s="77" t="s">
-        <v>456</v>
-      </c>
-      <c r="H162" s="78" t="s">
-        <v>457</v>
-      </c>
-      <c r="I162" s="77" t="s">
-        <v>458</v>
+      <c r="H166" s="98" t="s">
+        <v>464</v>
+      </c>
+      <c r="I166" s="99" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="167" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="96">
+        <v>2</v>
+      </c>
+      <c r="B167" s="96" t="s">
+        <v>229</v>
+      </c>
+      <c r="C167" s="97" t="s">
+        <v>465</v>
+      </c>
+      <c r="D167" s="97"/>
+      <c r="E167" s="97"/>
+      <c r="F167" s="96" t="s">
+        <v>463</v>
+      </c>
+      <c r="G167" s="96" t="s">
+        <v>229</v>
+      </c>
+      <c r="H167" s="98" t="s">
+        <v>464</v>
+      </c>
+      <c r="I167" s="99" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="168" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="96">
+        <v>3</v>
+      </c>
+      <c r="B168" s="96" t="s">
+        <v>229</v>
+      </c>
+      <c r="C168" s="97" t="s">
+        <v>466</v>
+      </c>
+      <c r="D168" s="97"/>
+      <c r="E168" s="97"/>
+      <c r="F168" s="96" t="s">
+        <v>467</v>
+      </c>
+      <c r="G168" s="96" t="s">
+        <v>229</v>
+      </c>
+      <c r="H168" s="98" t="s">
+        <v>468</v>
+      </c>
+      <c r="I168" s="99" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="169" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="96">
+        <v>4</v>
+      </c>
+      <c r="B169" s="96" t="s">
+        <v>229</v>
+      </c>
+      <c r="C169" s="97" t="s">
+        <v>469</v>
+      </c>
+      <c r="D169" s="97"/>
+      <c r="E169" s="97"/>
+      <c r="F169" s="96" t="s">
+        <v>467</v>
+      </c>
+      <c r="G169" s="96" t="s">
+        <v>229</v>
+      </c>
+      <c r="H169" s="98" t="s">
+        <v>468</v>
+      </c>
+      <c r="I169" s="99" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="170" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="96">
+        <v>5</v>
+      </c>
+      <c r="B170" s="96" t="s">
+        <v>229</v>
+      </c>
+      <c r="C170" s="97" t="s">
+        <v>470</v>
+      </c>
+      <c r="D170" s="97"/>
+      <c r="E170" s="97"/>
+      <c r="F170" s="96" t="s">
+        <v>14</v>
+      </c>
+      <c r="G170" s="96" t="s">
+        <v>229</v>
+      </c>
+      <c r="H170" s="98" t="s">
+        <v>471</v>
+      </c>
+      <c r="I170" s="99" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="171" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="96">
+        <v>6</v>
+      </c>
+      <c r="B171" s="96" t="s">
+        <v>229</v>
+      </c>
+      <c r="C171" s="97" t="s">
+        <v>472</v>
+      </c>
+      <c r="D171" s="97"/>
+      <c r="E171" s="97"/>
+      <c r="F171" s="96" t="s">
+        <v>14</v>
+      </c>
+      <c r="G171" s="96" t="s">
+        <v>229</v>
+      </c>
+      <c r="H171" s="98" t="s">
+        <v>471</v>
+      </c>
+      <c r="I171" s="99" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="172" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="100" t="s">
+        <v>229</v>
+      </c>
+      <c r="B172" s="100" t="s">
+        <v>229</v>
+      </c>
+      <c r="C172" s="100" t="s">
+        <v>473</v>
+      </c>
+      <c r="D172" s="100"/>
+      <c r="E172" s="100"/>
+      <c r="F172" s="100" t="s">
+        <v>229</v>
+      </c>
+      <c r="G172" s="100" t="s">
+        <v>229</v>
+      </c>
+      <c r="H172" s="101" t="s">
+        <v>474</v>
+      </c>
+      <c r="I172" s="100" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="174" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="102" t="s">
+        <v>229</v>
+      </c>
+      <c r="B174" s="102"/>
+      <c r="C174" s="102"/>
+      <c r="D174" s="102"/>
+      <c r="E174" s="102"/>
+      <c r="F174" s="102"/>
+      <c r="G174" s="102"/>
+      <c r="H174" s="102"/>
+      <c r="I174" s="102"/>
+    </row>
+    <row r="175" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="B175" s="103" t="s">
+        <v>229</v>
+      </c>
+      <c r="C175" s="103" t="s">
+        <v>475</v>
+      </c>
+      <c r="D175" s="103"/>
+      <c r="E175" s="103"/>
+      <c r="F175" s="103"/>
+      <c r="G175" s="103" t="s">
+        <v>476</v>
+      </c>
+      <c r="H175" s="103" t="s">
+        <v>477</v>
+      </c>
+      <c r="I175" s="103" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="176" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" s="104" t="s">
+        <v>229</v>
+      </c>
+      <c r="B176" s="104">
+        <v>1</v>
+      </c>
+      <c r="C176" s="105" t="s">
+        <v>479</v>
+      </c>
+      <c r="D176" s="105"/>
+      <c r="E176" s="105"/>
+      <c r="F176" s="105"/>
+      <c r="G176" s="106" t="s">
+        <v>480</v>
+      </c>
+      <c r="H176" s="107" t="s">
+        <v>481</v>
+      </c>
+      <c r="I176" s="108" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="177" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="104" t="s">
+        <v>229</v>
+      </c>
+      <c r="B177" s="104">
+        <v>2</v>
+      </c>
+      <c r="C177" s="105" t="s">
+        <v>483</v>
+      </c>
+      <c r="D177" s="105"/>
+      <c r="E177" s="105"/>
+      <c r="F177" s="105"/>
+      <c r="G177" s="106" t="s">
+        <v>484</v>
+      </c>
+      <c r="H177" s="107" t="s">
+        <v>485</v>
+      </c>
+      <c r="I177" s="108" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="178" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="104" t="s">
+        <v>229</v>
+      </c>
+      <c r="B178" s="104">
+        <v>3</v>
+      </c>
+      <c r="C178" s="105" t="s">
+        <v>486</v>
+      </c>
+      <c r="D178" s="105"/>
+      <c r="E178" s="105"/>
+      <c r="F178" s="105"/>
+      <c r="G178" s="106" t="s">
+        <v>487</v>
+      </c>
+      <c r="H178" s="107" t="s">
+        <v>485</v>
+      </c>
+      <c r="I178" s="108" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="179" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="104" t="s">
+        <v>229</v>
+      </c>
+      <c r="B179" s="104">
+        <v>4</v>
+      </c>
+      <c r="C179" s="105" t="s">
+        <v>488</v>
+      </c>
+      <c r="D179" s="105"/>
+      <c r="E179" s="105"/>
+      <c r="F179" s="105"/>
+      <c r="G179" s="106" t="s">
+        <v>489</v>
+      </c>
+      <c r="H179" s="107" t="s">
+        <v>485</v>
+      </c>
+      <c r="I179" s="108" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="181" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="109" t="s">
+        <v>229</v>
+      </c>
+      <c r="B181" s="109" t="s">
+        <v>229</v>
+      </c>
+      <c r="C181" s="109" t="s">
+        <v>490</v>
+      </c>
+      <c r="D181" s="109"/>
+      <c r="E181" s="109"/>
+      <c r="F181" s="109"/>
+      <c r="G181" s="110" t="s">
+        <v>491</v>
+      </c>
+      <c r="H181" s="111" t="s">
+        <v>481</v>
+      </c>
+      <c r="I181" s="112" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="183" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>229</v>
+      </c>
+      <c r="B183" t="s">
+        <v>229</v>
+      </c>
+      <c r="C183" t="s">
+        <v>229</v>
+      </c>
+      <c r="D183" s="113" t="s">
+        <v>493</v>
+      </c>
+      <c r="E183" s="113"/>
+      <c r="F183" s="113"/>
+      <c r="G183" t="s">
+        <v>229</v>
+      </c>
+      <c r="H183" s="114" t="s">
+        <v>481</v>
+      </c>
+      <c r="I183" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="184" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>229</v>
+      </c>
+      <c r="B184" t="s">
+        <v>229</v>
+      </c>
+      <c r="C184" t="s">
+        <v>229</v>
+      </c>
+      <c r="D184" s="115" t="s">
+        <v>494</v>
+      </c>
+      <c r="E184" s="115"/>
+      <c r="F184" s="115"/>
+      <c r="G184" t="s">
+        <v>229</v>
+      </c>
+      <c r="H184" s="116" t="s">
+        <v>492</v>
+      </c>
+      <c r="I184" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="147">
+  <mergeCells count="161">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="B3:B8"/>
@@ -6167,7 +6880,6 @@
     <mergeCell ref="G52:G55"/>
     <mergeCell ref="H52:H55"/>
     <mergeCell ref="I52:I55"/>
-    <mergeCell ref="C56:F56"/>
     <mergeCell ref="A58:I58"/>
     <mergeCell ref="A59:A62"/>
     <mergeCell ref="B59:B62"/>
@@ -6214,7 +6926,6 @@
     <mergeCell ref="G102:G106"/>
     <mergeCell ref="H102:H106"/>
     <mergeCell ref="I102:I106"/>
-    <mergeCell ref="C107:F107"/>
     <mergeCell ref="A109:I109"/>
     <mergeCell ref="A110:A115"/>
     <mergeCell ref="B110:B115"/>
@@ -6261,8 +6972,24 @@
     <mergeCell ref="G155:G160"/>
     <mergeCell ref="H155:H160"/>
     <mergeCell ref="I155:I160"/>
-    <mergeCell ref="C161:F161"/>
-    <mergeCell ref="C162:F162"/>
+    <mergeCell ref="A164:I164"/>
+    <mergeCell ref="C165:E165"/>
+    <mergeCell ref="C166:E166"/>
+    <mergeCell ref="C167:E167"/>
+    <mergeCell ref="C168:E168"/>
+    <mergeCell ref="C169:E169"/>
+    <mergeCell ref="C170:E170"/>
+    <mergeCell ref="C171:E171"/>
+    <mergeCell ref="C172:E172"/>
+    <mergeCell ref="A174:I174"/>
+    <mergeCell ref="C175:F175"/>
+    <mergeCell ref="C176:F176"/>
+    <mergeCell ref="C177:F177"/>
+    <mergeCell ref="C178:F178"/>
+    <mergeCell ref="C179:F179"/>
+    <mergeCell ref="C181:F181"/>
+    <mergeCell ref="D183:F183"/>
+    <mergeCell ref="D184:F184"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -6271,7 +6998,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -6280,1047 +7007,1026 @@
     <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="80" t="s">
-        <v>459</v>
-      </c>
-      <c r="D2" s="80" t="s">
-        <v>460</v>
-      </c>
-      <c r="E2" s="80" t="s">
-        <v>461</v>
-      </c>
-      <c r="F2" s="80" t="s">
-        <v>462</v>
-      </c>
-      <c r="G2" s="80" t="s">
-        <v>463</v>
-      </c>
-      <c r="H2" s="80" t="s">
+      <c r="C2" s="118" t="s">
+        <v>495</v>
+      </c>
+      <c r="D2" s="118" t="s">
+        <v>496</v>
+      </c>
+      <c r="E2" s="118" t="s">
+        <v>497</v>
+      </c>
+      <c r="F2" s="118" t="s">
+        <v>498</v>
+      </c>
+      <c r="G2" s="118" t="s">
+        <v>499</v>
+      </c>
+      <c r="H2" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="118" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="81">
+      <c r="A3" s="119">
         <v>16</v>
       </c>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="120" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="83" t="s">
-        <v>464</v>
-      </c>
-      <c r="D3" s="83" t="s">
-        <v>465</v>
-      </c>
-      <c r="E3" s="83" t="s">
-        <v>466</v>
-      </c>
-      <c r="F3" s="83" t="s">
-        <v>467</v>
-      </c>
-      <c r="G3" s="81" t="s">
+      <c r="C3" s="121" t="s">
+        <v>500</v>
+      </c>
+      <c r="D3" s="121" t="s">
+        <v>501</v>
+      </c>
+      <c r="E3" s="121" t="s">
+        <v>502</v>
+      </c>
+      <c r="F3" s="121" t="s">
+        <v>503</v>
+      </c>
+      <c r="G3" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="84" t="s">
+      <c r="H3" s="122" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="123" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="81">
+      <c r="A4" s="119">
         <v>2</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="83" t="s">
-        <v>468</v>
-      </c>
-      <c r="D4" s="83" t="s">
-        <v>469</v>
-      </c>
-      <c r="E4" s="83" t="s">
-        <v>470</v>
-      </c>
-      <c r="F4" s="83" t="s">
-        <v>471</v>
-      </c>
-      <c r="G4" s="81" t="s">
+      <c r="C4" s="121" t="s">
+        <v>504</v>
+      </c>
+      <c r="D4" s="121" t="s">
+        <v>505</v>
+      </c>
+      <c r="E4" s="121" t="s">
+        <v>506</v>
+      </c>
+      <c r="F4" s="121" t="s">
+        <v>507</v>
+      </c>
+      <c r="G4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="84" t="s">
+      <c r="H4" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="123" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="81">
+      <c r="A5" s="119">
         <v>5</v>
       </c>
-      <c r="B5" s="82" t="s">
+      <c r="B5" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="83" t="s">
-        <v>472</v>
-      </c>
-      <c r="D5" s="83" t="s">
-        <v>473</v>
-      </c>
-      <c r="E5" s="83" t="s">
-        <v>474</v>
-      </c>
-      <c r="F5" s="83" t="s">
-        <v>471</v>
-      </c>
-      <c r="G5" s="81" t="s">
+      <c r="C5" s="121" t="s">
+        <v>508</v>
+      </c>
+      <c r="D5" s="121" t="s">
+        <v>509</v>
+      </c>
+      <c r="E5" s="121" t="s">
+        <v>510</v>
+      </c>
+      <c r="F5" s="121" t="s">
+        <v>507</v>
+      </c>
+      <c r="G5" s="119" t="s">
         <v>60</v>
       </c>
-      <c r="H5" s="84" t="s">
+      <c r="H5" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="123" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="81">
+      <c r="A6" s="119">
         <v>9</v>
       </c>
-      <c r="B6" s="82" t="s">
+      <c r="B6" s="120" t="s">
         <v>88</v>
       </c>
-      <c r="C6" s="83" t="s">
-        <v>475</v>
-      </c>
-      <c r="D6" s="83" t="s">
-        <v>476</v>
-      </c>
-      <c r="E6" s="83" t="s">
-        <v>477</v>
-      </c>
-      <c r="F6" s="83" t="s">
-        <v>478</v>
-      </c>
-      <c r="G6" s="81" t="s">
+      <c r="C6" s="121" t="s">
+        <v>511</v>
+      </c>
+      <c r="D6" s="121" t="s">
+        <v>512</v>
+      </c>
+      <c r="E6" s="121" t="s">
+        <v>513</v>
+      </c>
+      <c r="F6" s="121" t="s">
+        <v>514</v>
+      </c>
+      <c r="G6" s="119" t="s">
         <v>93</v>
       </c>
-      <c r="H6" s="84" t="s">
+      <c r="H6" s="122" t="s">
+        <v>94</v>
+      </c>
+      <c r="I6" s="123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="119">
+        <v>7</v>
+      </c>
+      <c r="B7" s="120" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="121" t="s">
+        <v>515</v>
+      </c>
+      <c r="D7" s="121" t="s">
+        <v>516</v>
+      </c>
+      <c r="E7" s="121" t="s">
+        <v>517</v>
+      </c>
+      <c r="F7" s="121" t="s">
+        <v>518</v>
+      </c>
+      <c r="G7" s="119" t="s">
+        <v>116</v>
+      </c>
+      <c r="H7" s="122" t="s">
+        <v>117</v>
+      </c>
+      <c r="I7" s="123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="119">
+        <v>3</v>
+      </c>
+      <c r="B8" s="120" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="121" t="s">
+        <v>519</v>
+      </c>
+      <c r="D8" s="121" t="s">
+        <v>520</v>
+      </c>
+      <c r="E8" s="121" t="s">
+        <v>521</v>
+      </c>
+      <c r="F8" s="121" t="s">
+        <v>522</v>
+      </c>
+      <c r="G8" s="119" t="s">
+        <v>143</v>
+      </c>
+      <c r="H8" s="122" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" s="123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="119">
+        <v>11</v>
+      </c>
+      <c r="B9" s="120" t="s">
+        <v>160</v>
+      </c>
+      <c r="C9" s="121" t="s">
+        <v>523</v>
+      </c>
+      <c r="D9" s="121" t="s">
+        <v>524</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>525</v>
+      </c>
+      <c r="F9" s="121" t="s">
+        <v>526</v>
+      </c>
+      <c r="G9" s="119" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="122" t="s">
+        <v>166</v>
+      </c>
+      <c r="I9" s="123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="119">
+        <v>19</v>
+      </c>
+      <c r="B10" s="120" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" s="121" t="s">
+        <v>527</v>
+      </c>
+      <c r="D10" s="121" t="s">
+        <v>528</v>
+      </c>
+      <c r="E10" s="121" t="s">
+        <v>529</v>
+      </c>
+      <c r="F10" s="121" t="s">
+        <v>530</v>
+      </c>
+      <c r="G10" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="H10" s="122" t="s">
+        <v>166</v>
+      </c>
+      <c r="I10" s="123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="119">
+        <v>15</v>
+      </c>
+      <c r="B11" s="120" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="121" t="s">
+        <v>531</v>
+      </c>
+      <c r="D11" s="121" t="s">
+        <v>532</v>
+      </c>
+      <c r="E11" s="121" t="s">
+        <v>533</v>
+      </c>
+      <c r="F11" s="121" t="s">
+        <v>534</v>
+      </c>
+      <c r="G11" s="119" t="s">
+        <v>196</v>
+      </c>
+      <c r="H11" s="122" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="119">
+        <v>1</v>
+      </c>
+      <c r="B12" s="120" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12" s="121" t="s">
+        <v>535</v>
+      </c>
+      <c r="D12" s="121" t="s">
+        <v>536</v>
+      </c>
+      <c r="E12" s="121" t="s">
+        <v>537</v>
+      </c>
+      <c r="F12" s="121" t="s">
+        <v>538</v>
+      </c>
+      <c r="G12" s="119" t="s">
+        <v>219</v>
+      </c>
+      <c r="H12" s="122" t="s">
+        <v>220</v>
+      </c>
+      <c r="I12" s="123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="124" t="s">
+        <v>229</v>
+      </c>
+      <c r="B13" s="124" t="s">
+        <v>539</v>
+      </c>
+      <c r="C13" s="124" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" s="124"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="124" t="s">
+        <v>234</v>
+      </c>
+      <c r="H13" s="125" t="s">
+        <v>235</v>
+      </c>
+      <c r="I13" s="124" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="114" t="s">
+        <v>237</v>
+      </c>
+      <c r="B15" s="114"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="114"/>
+    </row>
+    <row r="16" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="126" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="126" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="126" t="s">
+        <v>495</v>
+      </c>
+      <c r="D16" s="126" t="s">
+        <v>496</v>
+      </c>
+      <c r="E16" s="126" t="s">
+        <v>497</v>
+      </c>
+      <c r="F16" s="126" t="s">
+        <v>498</v>
+      </c>
+      <c r="G16" s="126" t="s">
+        <v>499</v>
+      </c>
+      <c r="H16" s="126" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="126" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="119">
+        <v>6</v>
+      </c>
+      <c r="B17" s="120" t="s">
+        <v>238</v>
+      </c>
+      <c r="C17" s="121" t="s">
+        <v>540</v>
+      </c>
+      <c r="D17" s="121" t="s">
+        <v>541</v>
+      </c>
+      <c r="E17" s="121" t="s">
+        <v>542</v>
+      </c>
+      <c r="F17" s="121" t="s">
+        <v>543</v>
+      </c>
+      <c r="G17" s="119" t="s">
+        <v>242</v>
+      </c>
+      <c r="H17" s="122" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I17" s="123" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="81">
+    <row r="18" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="119">
+        <v>4</v>
+      </c>
+      <c r="B18" s="120" t="s">
+        <v>251</v>
+      </c>
+      <c r="C18" s="121" t="s">
+        <v>544</v>
+      </c>
+      <c r="D18" s="121" t="s">
+        <v>545</v>
+      </c>
+      <c r="E18" s="121" t="s">
+        <v>546</v>
+      </c>
+      <c r="F18" s="121" t="s">
+        <v>547</v>
+      </c>
+      <c r="G18" s="119" t="s">
+        <v>256</v>
+      </c>
+      <c r="H18" s="122" t="s">
+        <v>257</v>
+      </c>
+      <c r="I18" s="123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="119">
+        <v>5</v>
+      </c>
+      <c r="B19" s="120" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="121" t="s">
+        <v>508</v>
+      </c>
+      <c r="D19" s="121" t="s">
+        <v>548</v>
+      </c>
+      <c r="E19" s="121" t="s">
+        <v>549</v>
+      </c>
+      <c r="F19" s="121" t="s">
+        <v>550</v>
+      </c>
+      <c r="G19" s="119" t="s">
+        <v>282</v>
+      </c>
+      <c r="H19" s="122" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="119">
+        <v>14</v>
+      </c>
+      <c r="B20" s="120" t="s">
+        <v>283</v>
+      </c>
+      <c r="C20" s="121" t="s">
+        <v>551</v>
+      </c>
+      <c r="D20" s="121" t="s">
+        <v>552</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>553</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>526</v>
+      </c>
+      <c r="G20" s="119" t="s">
+        <v>288</v>
+      </c>
+      <c r="H20" s="122" t="s">
+        <v>289</v>
+      </c>
+      <c r="I20" s="123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="119">
+        <v>13</v>
+      </c>
+      <c r="B21" s="120" t="s">
+        <v>298</v>
+      </c>
+      <c r="C21" s="121" t="s">
+        <v>554</v>
+      </c>
+      <c r="D21" s="121" t="s">
+        <v>555</v>
+      </c>
+      <c r="E21" s="121" t="s">
+        <v>556</v>
+      </c>
+      <c r="F21" s="121" t="s">
+        <v>507</v>
+      </c>
+      <c r="G21" s="119" t="s">
+        <v>303</v>
+      </c>
+      <c r="H21" s="122" t="s">
+        <v>166</v>
+      </c>
+      <c r="I21" s="127" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="119">
+        <v>16</v>
+      </c>
+      <c r="B22" s="120" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="121" t="s">
+        <v>500</v>
+      </c>
+      <c r="D22" s="121" t="s">
+        <v>557</v>
+      </c>
+      <c r="E22" s="121" t="s">
+        <v>558</v>
+      </c>
+      <c r="F22" s="121" t="s">
+        <v>559</v>
+      </c>
+      <c r="G22" s="119" t="s">
+        <v>315</v>
+      </c>
+      <c r="H22" s="122" t="s">
+        <v>289</v>
+      </c>
+      <c r="I22" s="123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="119">
+        <v>1</v>
+      </c>
+      <c r="B23" s="120" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="121" t="s">
+        <v>535</v>
+      </c>
+      <c r="D23" s="121" t="s">
+        <v>560</v>
+      </c>
+      <c r="E23" s="121" t="s">
+        <v>561</v>
+      </c>
+      <c r="F23" s="121" t="s">
+        <v>562</v>
+      </c>
+      <c r="G23" s="119" t="s">
+        <v>316</v>
+      </c>
+      <c r="H23" s="122" t="s">
+        <v>317</v>
+      </c>
+      <c r="I23" s="123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="119">
+        <v>15</v>
+      </c>
+      <c r="B24" s="120" t="s">
+        <v>191</v>
+      </c>
+      <c r="C24" s="121" t="s">
+        <v>531</v>
+      </c>
+      <c r="D24" s="121" t="s">
+        <v>563</v>
+      </c>
+      <c r="E24" s="121" t="s">
+        <v>564</v>
+      </c>
+      <c r="F24" s="121" t="s">
+        <v>565</v>
+      </c>
+      <c r="G24" s="119" t="s">
+        <v>318</v>
+      </c>
+      <c r="H24" s="122" t="s">
+        <v>166</v>
+      </c>
+      <c r="I24" s="127" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="119">
+        <v>18</v>
+      </c>
+      <c r="B25" s="120" t="s">
+        <v>319</v>
+      </c>
+      <c r="C25" s="121" t="s">
+        <v>566</v>
+      </c>
+      <c r="D25" s="121" t="s">
+        <v>567</v>
+      </c>
+      <c r="E25" s="121" t="s">
+        <v>568</v>
+      </c>
+      <c r="F25" s="121" t="s">
+        <v>569</v>
+      </c>
+      <c r="G25" s="119" t="s">
+        <v>323</v>
+      </c>
+      <c r="H25" s="122" t="s">
+        <v>144</v>
+      </c>
+      <c r="I25" s="127" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="128" t="s">
+        <v>229</v>
+      </c>
+      <c r="B26" s="128" t="s">
+        <v>570</v>
+      </c>
+      <c r="C26" s="128" t="s">
+        <v>336</v>
+      </c>
+      <c r="D26" s="128"/>
+      <c r="E26" s="128"/>
+      <c r="F26" s="128"/>
+      <c r="G26" s="128" t="s">
+        <v>339</v>
+      </c>
+      <c r="H26" s="129" t="s">
+        <v>340</v>
+      </c>
+      <c r="I26" s="128" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="130" t="s">
+        <v>342</v>
+      </c>
+      <c r="B28" s="130"/>
+      <c r="C28" s="130"/>
+      <c r="D28" s="130"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="130"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
+    </row>
+    <row r="29" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="131" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="131" t="s">
+        <v>495</v>
+      </c>
+      <c r="D29" s="131" t="s">
+        <v>496</v>
+      </c>
+      <c r="E29" s="131" t="s">
+        <v>497</v>
+      </c>
+      <c r="F29" s="131" t="s">
+        <v>498</v>
+      </c>
+      <c r="G29" s="131" t="s">
+        <v>499</v>
+      </c>
+      <c r="H29" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="82" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="83" t="s">
-        <v>479</v>
-      </c>
-      <c r="D7" s="83" t="s">
-        <v>480</v>
-      </c>
-      <c r="E7" s="83" t="s">
-        <v>481</v>
-      </c>
-      <c r="F7" s="83" t="s">
-        <v>482</v>
-      </c>
-      <c r="G7" s="81" t="s">
-        <v>115</v>
-      </c>
-      <c r="H7" s="84" t="s">
-        <v>116</v>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="I29" s="131" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="119">
+        <v>8</v>
+      </c>
+      <c r="B30" s="120" t="s">
+        <v>343</v>
+      </c>
+      <c r="C30" s="121" t="s">
+        <v>571</v>
+      </c>
+      <c r="D30" s="121" t="s">
+        <v>572</v>
+      </c>
+      <c r="E30" s="121" t="s">
+        <v>573</v>
+      </c>
+      <c r="F30" s="121" t="s">
+        <v>574</v>
+      </c>
+      <c r="G30" s="119" t="s">
+        <v>348</v>
+      </c>
+      <c r="H30" s="122" t="s">
+        <v>94</v>
+      </c>
+      <c r="I30" s="123" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="81">
-        <v>3</v>
-      </c>
-      <c r="B8" s="82" t="s">
-        <v>137</v>
-      </c>
-      <c r="C8" s="83" t="s">
-        <v>483</v>
-      </c>
-      <c r="D8" s="83" t="s">
-        <v>484</v>
-      </c>
-      <c r="E8" s="83" t="s">
-        <v>485</v>
-      </c>
-      <c r="F8" s="83" t="s">
-        <v>486</v>
-      </c>
-      <c r="G8" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="H8" s="84" t="s">
-        <v>143</v>
-      </c>
-      <c r="I8" s="7" t="s">
+    <row r="31" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="119">
+        <v>10</v>
+      </c>
+      <c r="B31" s="120" t="s">
+        <v>365</v>
+      </c>
+      <c r="C31" s="121" t="s">
+        <v>575</v>
+      </c>
+      <c r="D31" s="121" t="s">
+        <v>576</v>
+      </c>
+      <c r="E31" s="121" t="s">
+        <v>577</v>
+      </c>
+      <c r="F31" s="121" t="s">
+        <v>578</v>
+      </c>
+      <c r="G31" s="119" t="s">
+        <v>370</v>
+      </c>
+      <c r="H31" s="122" t="s">
+        <v>117</v>
+      </c>
+      <c r="I31" s="127" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="119">
+        <v>4</v>
+      </c>
+      <c r="B32" s="120" t="s">
+        <v>251</v>
+      </c>
+      <c r="C32" s="121" t="s">
+        <v>544</v>
+      </c>
+      <c r="D32" s="121" t="s">
+        <v>579</v>
+      </c>
+      <c r="E32" s="121" t="s">
+        <v>580</v>
+      </c>
+      <c r="F32" s="121" t="s">
+        <v>581</v>
+      </c>
+      <c r="G32" s="119" t="s">
+        <v>388</v>
+      </c>
+      <c r="H32" s="122" t="s">
+        <v>166</v>
+      </c>
+      <c r="I32" s="127" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="119">
+        <v>12</v>
+      </c>
+      <c r="B33" s="120" t="s">
+        <v>389</v>
+      </c>
+      <c r="C33" s="121" t="s">
+        <v>582</v>
+      </c>
+      <c r="D33" s="121" t="s">
+        <v>583</v>
+      </c>
+      <c r="E33" s="121" t="s">
+        <v>584</v>
+      </c>
+      <c r="F33" s="121" t="s">
+        <v>585</v>
+      </c>
+      <c r="G33" s="119" t="s">
+        <v>394</v>
+      </c>
+      <c r="H33" s="122" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="123" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="81">
-        <v>11</v>
-      </c>
-      <c r="B9" s="82" t="s">
-        <v>159</v>
-      </c>
-      <c r="C9" s="83" t="s">
-        <v>487</v>
-      </c>
-      <c r="D9" s="83" t="s">
-        <v>488</v>
-      </c>
-      <c r="E9" s="83" t="s">
-        <v>489</v>
-      </c>
-      <c r="F9" s="83" t="s">
-        <v>490</v>
-      </c>
-      <c r="G9" s="81" t="s">
-        <v>164</v>
-      </c>
-      <c r="H9" s="84" t="s">
-        <v>165</v>
-      </c>
-      <c r="I9" s="7" t="s">
+    <row r="34" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="119">
+        <v>16</v>
+      </c>
+      <c r="B34" s="120" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="121" t="s">
+        <v>500</v>
+      </c>
+      <c r="D34" s="121" t="s">
+        <v>586</v>
+      </c>
+      <c r="E34" s="121" t="s">
+        <v>587</v>
+      </c>
+      <c r="F34" s="121" t="s">
+        <v>588</v>
+      </c>
+      <c r="G34" s="119" t="s">
+        <v>410</v>
+      </c>
+      <c r="H34" s="122" t="s">
+        <v>289</v>
+      </c>
+      <c r="I34" s="127" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="35" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="119">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="81">
-        <v>19</v>
-      </c>
-      <c r="B10" s="82" t="s">
-        <v>177</v>
-      </c>
-      <c r="C10" s="83" t="s">
-        <v>491</v>
-      </c>
-      <c r="D10" s="83" t="s">
-        <v>492</v>
-      </c>
-      <c r="E10" s="83" t="s">
-        <v>493</v>
-      </c>
-      <c r="F10" s="83" t="s">
-        <v>494</v>
-      </c>
-      <c r="G10" s="81" t="s">
-        <v>180</v>
-      </c>
-      <c r="H10" s="84" t="s">
-        <v>165</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="81">
+      <c r="B35" s="120" t="s">
+        <v>411</v>
+      </c>
+      <c r="C35" s="121" t="s">
+        <v>589</v>
+      </c>
+      <c r="D35" s="121" t="s">
+        <v>590</v>
+      </c>
+      <c r="E35" s="121" t="s">
+        <v>591</v>
+      </c>
+      <c r="F35" s="121" t="s">
+        <v>592</v>
+      </c>
+      <c r="G35" s="119" t="s">
+        <v>416</v>
+      </c>
+      <c r="H35" s="122" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="127" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="36" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="119">
         <v>15</v>
       </c>
-      <c r="B11" s="82" t="s">
-        <v>190</v>
-      </c>
-      <c r="C11" s="83" t="s">
-        <v>495</v>
-      </c>
-      <c r="D11" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E11" s="83" t="s">
-        <v>497</v>
-      </c>
-      <c r="F11" s="83" t="s">
-        <v>498</v>
-      </c>
-      <c r="G11" s="81" t="s">
-        <v>195</v>
-      </c>
-      <c r="H11" s="84" t="s">
-        <v>196</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="81">
+      <c r="B36" s="120" t="s">
+        <v>191</v>
+      </c>
+      <c r="C36" s="121" t="s">
+        <v>531</v>
+      </c>
+      <c r="D36" s="121" t="s">
+        <v>593</v>
+      </c>
+      <c r="E36" s="121" t="s">
+        <v>594</v>
+      </c>
+      <c r="F36" s="121" t="s">
+        <v>588</v>
+      </c>
+      <c r="G36" s="119" t="s">
+        <v>428</v>
+      </c>
+      <c r="H36" s="122" t="s">
+        <v>166</v>
+      </c>
+      <c r="I36" s="127" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="37" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="119">
         <v>1</v>
       </c>
-      <c r="B12" s="82" t="s">
+      <c r="B37" s="120" t="s">
         <v>214</v>
       </c>
-      <c r="C12" s="83" t="s">
-        <v>499</v>
-      </c>
-      <c r="D12" s="83" t="s">
-        <v>500</v>
-      </c>
-      <c r="E12" s="83" t="s">
-        <v>501</v>
-      </c>
-      <c r="F12" s="83" t="s">
-        <v>502</v>
-      </c>
-      <c r="G12" s="81" t="s">
-        <v>219</v>
-      </c>
-      <c r="H12" s="84" t="s">
-        <v>220</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="36" t="s">
+      <c r="C37" s="121" t="s">
+        <v>535</v>
+      </c>
+      <c r="D37" s="121" t="s">
+        <v>595</v>
+      </c>
+      <c r="E37" s="121" t="s">
+        <v>596</v>
+      </c>
+      <c r="F37" s="121" t="s">
+        <v>597</v>
+      </c>
+      <c r="G37" s="119" t="s">
+        <v>429</v>
+      </c>
+      <c r="H37" s="122" t="s">
+        <v>317</v>
+      </c>
+      <c r="I37" s="127" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="38" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="119">
+        <v>20</v>
+      </c>
+      <c r="B38" s="120" t="s">
+        <v>430</v>
+      </c>
+      <c r="C38" s="121" t="s">
+        <v>598</v>
+      </c>
+      <c r="D38" s="121" t="s">
+        <v>599</v>
+      </c>
+      <c r="E38" s="121" t="s">
+        <v>600</v>
+      </c>
+      <c r="F38" s="121" t="s">
+        <v>601</v>
+      </c>
+      <c r="G38" s="119" t="s">
+        <v>433</v>
+      </c>
+      <c r="H38" s="122" t="s">
+        <v>434</v>
+      </c>
+      <c r="I38" s="127" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="132" t="s">
         <v>229</v>
       </c>
-      <c r="B13" s="36" t="s">
-        <v>503</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36" t="s">
-        <v>232</v>
-      </c>
-      <c r="H13" s="85" t="s">
-        <v>233</v>
-      </c>
-      <c r="I13" s="36" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="86" t="s">
-        <v>235</v>
-      </c>
-      <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="86"/>
-      <c r="H15" s="86"/>
-      <c r="I15" s="86"/>
-    </row>
-    <row r="16" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="87" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="87" t="s">
-        <v>459</v>
-      </c>
-      <c r="D16" s="87" t="s">
-        <v>460</v>
-      </c>
-      <c r="E16" s="87" t="s">
-        <v>461</v>
-      </c>
-      <c r="F16" s="87" t="s">
-        <v>462</v>
-      </c>
-      <c r="G16" s="87" t="s">
-        <v>463</v>
-      </c>
-      <c r="H16" s="87" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" s="87" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="81">
-        <v>6</v>
-      </c>
-      <c r="B17" s="82" t="s">
-        <v>236</v>
-      </c>
-      <c r="C17" s="83" t="s">
-        <v>504</v>
-      </c>
-      <c r="D17" s="83" t="s">
-        <v>505</v>
-      </c>
-      <c r="E17" s="83" t="s">
-        <v>506</v>
-      </c>
-      <c r="F17" s="83" t="s">
-        <v>507</v>
-      </c>
-      <c r="G17" s="81" t="s">
-        <v>240</v>
-      </c>
-      <c r="H17" s="84" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="81">
-        <v>4</v>
-      </c>
-      <c r="B18" s="82" t="s">
-        <v>249</v>
-      </c>
-      <c r="C18" s="83" t="s">
-        <v>508</v>
-      </c>
-      <c r="D18" s="83" t="s">
-        <v>509</v>
-      </c>
-      <c r="E18" s="83" t="s">
-        <v>510</v>
-      </c>
-      <c r="F18" s="83" t="s">
-        <v>511</v>
-      </c>
-      <c r="G18" s="81" t="s">
-        <v>254</v>
-      </c>
-      <c r="H18" s="84" t="s">
-        <v>255</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="81">
-        <v>5</v>
-      </c>
-      <c r="B19" s="82" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="83" t="s">
-        <v>472</v>
-      </c>
-      <c r="D19" s="83" t="s">
-        <v>512</v>
-      </c>
-      <c r="E19" s="83" t="s">
-        <v>513</v>
-      </c>
-      <c r="F19" s="83" t="s">
-        <v>514</v>
-      </c>
-      <c r="G19" s="81" t="s">
-        <v>280</v>
-      </c>
-      <c r="H19" s="84" t="s">
-        <v>165</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="81">
-        <v>14</v>
-      </c>
-      <c r="B20" s="82" t="s">
-        <v>281</v>
-      </c>
-      <c r="C20" s="83" t="s">
-        <v>515</v>
-      </c>
-      <c r="D20" s="83" t="s">
-        <v>516</v>
-      </c>
-      <c r="E20" s="83" t="s">
-        <v>517</v>
-      </c>
-      <c r="F20" s="83" t="s">
-        <v>490</v>
-      </c>
-      <c r="G20" s="81" t="s">
-        <v>286</v>
-      </c>
-      <c r="H20" s="84" t="s">
-        <v>287</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="81">
-        <v>13</v>
-      </c>
-      <c r="B21" s="82" t="s">
-        <v>296</v>
-      </c>
-      <c r="C21" s="83" t="s">
-        <v>518</v>
-      </c>
-      <c r="D21" s="83" t="s">
-        <v>519</v>
-      </c>
-      <c r="E21" s="83" t="s">
-        <v>520</v>
-      </c>
-      <c r="F21" s="83" t="s">
-        <v>471</v>
-      </c>
-      <c r="G21" s="81" t="s">
-        <v>301</v>
-      </c>
-      <c r="H21" s="84" t="s">
-        <v>220</v>
-      </c>
-      <c r="I21" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="81">
-        <v>16</v>
-      </c>
-      <c r="B22" s="82" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="83" t="s">
-        <v>464</v>
-      </c>
-      <c r="D22" s="83" t="s">
-        <v>521</v>
-      </c>
-      <c r="E22" s="83" t="s">
-        <v>522</v>
-      </c>
-      <c r="F22" s="83" t="s">
-        <v>523</v>
-      </c>
-      <c r="G22" s="81" t="s">
-        <v>313</v>
-      </c>
-      <c r="H22" s="84" t="s">
-        <v>287</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="81">
-        <v>1</v>
-      </c>
-      <c r="B23" s="82" t="s">
-        <v>214</v>
-      </c>
-      <c r="C23" s="83" t="s">
-        <v>499</v>
-      </c>
-      <c r="D23" s="83" t="s">
-        <v>524</v>
-      </c>
-      <c r="E23" s="83" t="s">
-        <v>525</v>
-      </c>
-      <c r="F23" s="83" t="s">
-        <v>526</v>
-      </c>
-      <c r="G23" s="81" t="s">
-        <v>314</v>
-      </c>
-      <c r="H23" s="84" t="s">
-        <v>315</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="81">
-        <v>15</v>
-      </c>
-      <c r="B24" s="82" t="s">
-        <v>190</v>
-      </c>
-      <c r="C24" s="83" t="s">
-        <v>495</v>
-      </c>
-      <c r="D24" s="83" t="s">
-        <v>527</v>
-      </c>
-      <c r="E24" s="83" t="s">
-        <v>528</v>
-      </c>
-      <c r="F24" s="83" t="s">
-        <v>529</v>
-      </c>
-      <c r="G24" s="81" t="s">
-        <v>316</v>
-      </c>
-      <c r="H24" s="84" t="s">
-        <v>220</v>
-      </c>
-      <c r="I24" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="81">
-        <v>18</v>
-      </c>
-      <c r="B25" s="82" t="s">
-        <v>317</v>
-      </c>
-      <c r="C25" s="83" t="s">
-        <v>530</v>
-      </c>
-      <c r="D25" s="83" t="s">
-        <v>531</v>
-      </c>
-      <c r="E25" s="83" t="s">
-        <v>532</v>
-      </c>
-      <c r="F25" s="83" t="s">
-        <v>533</v>
-      </c>
-      <c r="G25" s="81" t="s">
-        <v>321</v>
-      </c>
-      <c r="H25" s="84" t="s">
-        <v>322</v>
-      </c>
-      <c r="I25" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="B26" s="52" t="s">
-        <v>534</v>
-      </c>
-      <c r="C26" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52" t="s">
-        <v>336</v>
-      </c>
-      <c r="H26" s="88" t="s">
-        <v>337</v>
-      </c>
-      <c r="I26" s="52" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="89" t="s">
-        <v>339</v>
-      </c>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-    </row>
-    <row r="29" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="90" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="90" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="90" t="s">
-        <v>459</v>
-      </c>
-      <c r="D29" s="90" t="s">
-        <v>460</v>
-      </c>
-      <c r="E29" s="90" t="s">
-        <v>461</v>
-      </c>
-      <c r="F29" s="90" t="s">
-        <v>462</v>
-      </c>
-      <c r="G29" s="90" t="s">
-        <v>463</v>
-      </c>
-      <c r="H29" s="90" t="s">
-        <v>7</v>
-      </c>
-      <c r="I29" s="90" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="81">
-        <v>8</v>
-      </c>
-      <c r="B30" s="82" t="s">
-        <v>340</v>
-      </c>
-      <c r="C30" s="83" t="s">
-        <v>535</v>
-      </c>
-      <c r="D30" s="83" t="s">
-        <v>536</v>
-      </c>
-      <c r="E30" s="83" t="s">
-        <v>537</v>
-      </c>
-      <c r="F30" s="83" t="s">
-        <v>538</v>
-      </c>
-      <c r="G30" s="81" t="s">
-        <v>345</v>
-      </c>
-      <c r="H30" s="84" t="s">
-        <v>346</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="81">
-        <v>10</v>
-      </c>
-      <c r="B31" s="82" t="s">
-        <v>363</v>
-      </c>
-      <c r="C31" s="83" t="s">
-        <v>539</v>
-      </c>
-      <c r="D31" s="83" t="s">
-        <v>540</v>
-      </c>
-      <c r="E31" s="83" t="s">
-        <v>541</v>
-      </c>
-      <c r="F31" s="83" t="s">
-        <v>542</v>
-      </c>
-      <c r="G31" s="81" t="s">
-        <v>368</v>
-      </c>
-      <c r="H31" s="84" t="s">
-        <v>369</v>
-      </c>
-      <c r="I31" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="32" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="81">
-        <v>4</v>
-      </c>
-      <c r="B32" s="82" t="s">
-        <v>249</v>
-      </c>
-      <c r="C32" s="83" t="s">
-        <v>508</v>
-      </c>
-      <c r="D32" s="83" t="s">
-        <v>543</v>
-      </c>
-      <c r="E32" s="83" t="s">
-        <v>544</v>
-      </c>
-      <c r="F32" s="83" t="s">
-        <v>545</v>
-      </c>
-      <c r="G32" s="81" t="s">
-        <v>387</v>
-      </c>
-      <c r="H32" s="84" t="s">
-        <v>388</v>
-      </c>
-      <c r="I32" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="33" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="81">
-        <v>12</v>
-      </c>
-      <c r="B33" s="82" t="s">
-        <v>389</v>
-      </c>
-      <c r="C33" s="83" t="s">
-        <v>546</v>
-      </c>
-      <c r="D33" s="83" t="s">
-        <v>547</v>
-      </c>
-      <c r="E33" s="83" t="s">
-        <v>548</v>
-      </c>
-      <c r="F33" s="83" t="s">
-        <v>549</v>
-      </c>
-      <c r="G33" s="81" t="s">
-        <v>394</v>
-      </c>
-      <c r="H33" s="84" t="s">
-        <v>322</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="81">
-        <v>16</v>
-      </c>
-      <c r="B34" s="82" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="83" t="s">
-        <v>464</v>
-      </c>
-      <c r="D34" s="83" t="s">
-        <v>550</v>
-      </c>
-      <c r="E34" s="83" t="s">
-        <v>551</v>
-      </c>
-      <c r="F34" s="83" t="s">
-        <v>552</v>
-      </c>
-      <c r="G34" s="81" t="s">
-        <v>410</v>
-      </c>
-      <c r="H34" s="84" t="s">
-        <v>411</v>
-      </c>
-      <c r="I34" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="35" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="81">
-        <v>17</v>
-      </c>
-      <c r="B35" s="82" t="s">
-        <v>412</v>
-      </c>
-      <c r="C35" s="83" t="s">
-        <v>553</v>
-      </c>
-      <c r="D35" s="83" t="s">
-        <v>554</v>
-      </c>
-      <c r="E35" s="83" t="s">
-        <v>555</v>
-      </c>
-      <c r="F35" s="83" t="s">
-        <v>556</v>
-      </c>
-      <c r="G35" s="81" t="s">
-        <v>417</v>
-      </c>
-      <c r="H35" s="84" t="s">
-        <v>418</v>
-      </c>
-      <c r="I35" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="36" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="81">
-        <v>15</v>
-      </c>
-      <c r="B36" s="82" t="s">
-        <v>190</v>
-      </c>
-      <c r="C36" s="83" t="s">
-        <v>495</v>
-      </c>
-      <c r="D36" s="83" t="s">
-        <v>557</v>
-      </c>
-      <c r="E36" s="83" t="s">
-        <v>558</v>
-      </c>
-      <c r="F36" s="83" t="s">
-        <v>552</v>
-      </c>
-      <c r="G36" s="81" t="s">
-        <v>430</v>
-      </c>
-      <c r="H36" s="84" t="s">
-        <v>165</v>
-      </c>
-      <c r="I36" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="37" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="81">
-        <v>1</v>
-      </c>
-      <c r="B37" s="82" t="s">
-        <v>214</v>
-      </c>
-      <c r="C37" s="83" t="s">
-        <v>499</v>
-      </c>
-      <c r="D37" s="83" t="s">
-        <v>559</v>
-      </c>
-      <c r="E37" s="83" t="s">
-        <v>560</v>
-      </c>
-      <c r="F37" s="83" t="s">
-        <v>561</v>
-      </c>
-      <c r="G37" s="81" t="s">
-        <v>431</v>
-      </c>
-      <c r="H37" s="84" t="s">
-        <v>315</v>
-      </c>
-      <c r="I37" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="38" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="81">
-        <v>20</v>
-      </c>
-      <c r="B38" s="82" t="s">
-        <v>432</v>
-      </c>
-      <c r="C38" s="83" t="s">
-        <v>562</v>
-      </c>
-      <c r="D38" s="83" t="s">
-        <v>563</v>
-      </c>
-      <c r="E38" s="83" t="s">
-        <v>564</v>
-      </c>
-      <c r="F38" s="83" t="s">
-        <v>565</v>
-      </c>
-      <c r="G38" s="81" t="s">
-        <v>435</v>
-      </c>
-      <c r="H38" s="84" t="s">
-        <v>436</v>
-      </c>
-      <c r="I38" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="75" t="s">
-        <v>229</v>
-      </c>
-      <c r="B39" s="75" t="s">
-        <v>534</v>
-      </c>
-      <c r="C39" s="75" t="s">
-        <v>450</v>
-      </c>
-      <c r="D39" s="75"/>
-      <c r="E39" s="75"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="75" t="s">
+      <c r="B39" s="132" t="s">
+        <v>570</v>
+      </c>
+      <c r="C39" s="132" t="s">
+        <v>448</v>
+      </c>
+      <c r="D39" s="132"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="132"/>
+      <c r="G39" s="132" t="s">
         <v>451</v>
       </c>
-      <c r="H39" s="91" t="s">
+      <c r="H39" s="133" t="s">
         <v>452</v>
       </c>
-      <c r="I39" s="75" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="92" t="s">
-        <v>229</v>
-      </c>
-      <c r="B41" s="92" t="s">
-        <v>454</v>
-      </c>
-      <c r="C41" s="92"/>
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="92" t="s">
-        <v>566</v>
-      </c>
-      <c r="H41" s="93" t="s">
-        <v>457</v>
-      </c>
-      <c r="I41" s="92" t="s">
-        <v>229</v>
+      <c r="I39" s="132" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="C39:F39"/>
-    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
